--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.1 App_Inspección_Resp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Inspeccion Labores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB4277-E8EF-43A2-94E2-A37ACEF4220B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C45E21-58A5-473B-AF33-D44AF2A4B2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="302">
   <si>
     <t>YR_1016_GA9697W</t>
   </si>
@@ -849,13 +849,106 @@
   </si>
   <si>
     <t>Actividad / 活动</t>
+  </si>
+  <si>
+    <t>Finality / 目的</t>
+  </si>
+  <si>
+    <t>Ore / 矿石</t>
+  </si>
+  <si>
+    <t>Ventilation chamber / 通风室</t>
+  </si>
+  <si>
+    <t>Access / 使用权</t>
+  </si>
+  <si>
+    <t>Borehole chamber / 钻孔室</t>
+  </si>
+  <si>
+    <t>Ramp conecction / 坡道连接</t>
+  </si>
+  <si>
+    <t>Exploration drilling rig / 勘探钻井平台</t>
+  </si>
+  <si>
+    <t>Sump type B / B型油底壳</t>
+  </si>
+  <si>
+    <t>Footwall / 墙底</t>
+  </si>
+  <si>
+    <t>Ramp / 坡道</t>
+  </si>
+  <si>
+    <t>Ramp by pass / 匝道绕行</t>
+  </si>
+  <si>
+    <t>Workshop Chamber / 工作坊</t>
+  </si>
+  <si>
+    <t>Sump type A1 / A1型油底壳</t>
+  </si>
+  <si>
+    <t>Active / 积极的</t>
+  </si>
+  <si>
+    <t>Duver Gómez</t>
+  </si>
+  <si>
+    <t>Access to San Antonio / 通往圣安东尼奥的通道</t>
+  </si>
+  <si>
+    <t>Access to Athenea / 通往雅典娜的通道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borehole chamber / 钻孔室 </t>
+  </si>
+  <si>
+    <t>Electrical substation / 变电站</t>
+  </si>
+  <si>
+    <t>Ventilation chamber /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To improve stope production / 提高采场产量 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access / 通道 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sump type B / B型集水坑 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access and ventilation RB infraestructure / RB型通风基础设施通道和通风 </t>
+  </si>
+  <si>
+    <t>Connection between levels / 楼层间连接</t>
+  </si>
+  <si>
+    <t>Access / 通道</t>
+  </si>
+  <si>
+    <t>Ramp by pass / 旁路坡道</t>
+  </si>
+  <si>
+    <t>Sump type B / B型集水坑</t>
+  </si>
+  <si>
+    <t>Footwal / 人行道</t>
+  </si>
+  <si>
+    <t>Workshop Chamber / 车间</t>
+  </si>
+  <si>
+    <t>conecction with / 连接</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -935,6 +1028,24 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -962,7 +1073,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1003,11 +1114,29 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="22">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1311,7 +1440,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D439787B-8AF9-437A-ACA3-9AE721EC9057}" name="Table1" displayName="Table1" ref="C1:C8" totalsRowShown="0" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D439787B-8AF9-437A-ACA3-9AE721EC9057}" name="Table1" displayName="Table1" ref="C1:C8" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="C1:C8" xr:uid="{70DB07E2-C002-4DE0-B33B-D15BCFD1C0FD}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{144D0974-502C-47C7-ACBE-1D9AF36F72AF}" name="Inspector / 检查员"/>
@@ -1321,17 +1450,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EDAB2EE4-CE01-46C9-9FD8-0A4603DCE229}" name="Table2" displayName="Table2" ref="E1:E3" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EDAB2EE4-CE01-46C9-9FD8-0A4603DCE229}" name="Table2" displayName="Table2" ref="E1:E3" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="E1:E3" xr:uid="{08120ED6-A344-42E4-99F3-B028DE51A254}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{46527FCD-D912-4257-9D59-7A1BE52E90D5}" name="Shift / 班" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{46527FCD-D912-4257-9D59-7A1BE52E90D5}" name="Shift / 班" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03090CE9-5A50-4B9C-B628-1780F2665F2D}" name="Table3" displayName="Table3" ref="G1:G3" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{03090CE9-5A50-4B9C-B628-1780F2665F2D}" name="Table3" displayName="Table3" ref="G1:G3" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="G1:G3" xr:uid="{C6EFD98B-196E-472D-8C2A-4624785D0DA4}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{74834B83-2A2A-493A-8306-0158856DB1BA}" name="Contractor / 承包商"/>
@@ -1341,51 +1470,53 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C312BA50-54AE-4C7A-83D1-B6B4A62C0B12}" name="Table4" displayName="Table4" ref="I1:I4" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C312BA50-54AE-4C7A-83D1-B6B4A62C0B12}" name="Table4" displayName="Table4" ref="I1:I4" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="I1:I4" xr:uid="{D849C58B-CB47-46D6-9253-546ADD1FD233}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6C5A0638-B5EF-495E-B6F0-4C710DF21422}" name="Guard / 警卫" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{6C5A0638-B5EF-495E-B6F0-4C710DF21422}" name="Guard / 警卫" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B2E4229F-B7AF-4171-AEBC-9ED5501D1C39}" name="Table5" displayName="Table5" ref="K1:K18" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="K1:K18" xr:uid="{3C40DFAE-BB38-4F10-8FAD-3B5403245976}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B2E4229F-B7AF-4171-AEBC-9ED5501D1C39}" name="Table5" displayName="Table5" ref="K1:K19" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="K1:K19" xr:uid="{3C40DFAE-BB38-4F10-8FAD-3B5403245976}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E13DC40-D66E-4558-A21A-B2F38072C8CD}" name="Supervisor / 导师" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{8E13DC40-D66E-4558-A21A-B2F38072C8CD}" name="Supervisor / 导师" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0E73902A-3F11-4486-8DDF-A75DAFF5B881}" name="Table6" displayName="Table6" ref="M1:O238" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0E73902A-3F11-4486-8DDF-A75DAFF5B881}" name="Table6" displayName="Table6" ref="M1:O238" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="M1:O238" xr:uid="{5772E2E4-9C53-439A-8D10-38CF55306BE8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F9010FA5-A011-4788-B978-6D7250B5E4AB}" name="Day / 天" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{F9010FA5-A011-4788-B978-6D7250B5E4AB}" name="Day / 天" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{E9AD6F2F-340D-4575-B951-5A207662E8F2}" name="Month / 月"/>
-    <tableColumn id="3" xr3:uid="{4F2EF4C3-E498-40A6-804A-C95E61ADD1E3}" name="Week / 星期" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{4F2EF4C3-E498-40A6-804A-C95E61ADD1E3}" name="Week / 星期" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{95A66A3D-2781-4D15-9287-8A2DF1FC1BE1}" name="Table7" displayName="Table7" ref="Q1:S505" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="Q1:S505" xr:uid="{203D5ED5-1884-4108-96D1-7F5CA0F25129}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{052932E4-8135-4269-BAC1-DA6D9B51531E}" name="Monthly plan / 月度计划" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{1E454E6B-FA17-4C23-A1A5-97034058D14E}" name="Size [m]" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{C518B170-2579-4222-8C22-112DF2598E61}" name="Meters Plan [m] / 平面图 [米]" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{95A66A3D-2781-4D15-9287-8A2DF1FC1BE1}" name="Table7" displayName="Table7" ref="Q1:U505" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="Q1:U505" xr:uid="{203D5ED5-1884-4108-96D1-7F5CA0F25129}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{052932E4-8135-4269-BAC1-DA6D9B51531E}" name="Monthly plan / 月度计划" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{1E454E6B-FA17-4C23-A1A5-97034058D14E}" name="Size [m]" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{C518B170-2579-4222-8C22-112DF2598E61}" name="Meters Plan [m] / 平面图 [米]" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{D876DBDD-DA6E-499D-8547-A3ED4B6952B3}" name="Finality / 目的" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{05741128-2EFF-4F9E-9063-A88A2D31B45C}" name="Active / 积极的" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A22563B3-A5D8-4758-B0C1-7BFE0EEA4992}" name="Table8" displayName="Table8" ref="A1:A54" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A22563B3-A5D8-4758-B0C1-7BFE0EEA4992}" name="Table8" displayName="Table8" ref="A1:A54" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:A54" xr:uid="{A22563B3-A5D8-4758-B0C1-7BFE0EEA4992}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{4901CBE7-8E37-4469-A963-28C214C7ADA2}" name="Actividad / 活动"/>
@@ -1673,9 +1804,12 @@
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="63.21875" customWidth="1"/>
+    <col min="23" max="23" width="45.21875" customWidth="1"/>
+    <col min="24" max="24" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>270</v>
       </c>
@@ -1712,8 +1846,14 @@
       <c r="S1" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>157</v>
       </c>
@@ -1746,8 +1886,10 @@
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>158</v>
       </c>
@@ -1780,8 +1922,12 @@
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>159</v>
       </c>
@@ -1808,8 +1954,12 @@
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>160</v>
       </c>
@@ -1833,8 +1983,12 @@
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>161</v>
       </c>
@@ -1858,8 +2012,12 @@
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T6" s="1"/>
+      <c r="U6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>162</v>
       </c>
@@ -1883,8 +2041,12 @@
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T7" s="1"/>
+      <c r="U7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -1908,8 +2070,12 @@
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T8" s="1"/>
+      <c r="U8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>164</v>
       </c>
@@ -1930,8 +2096,12 @@
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T9" s="1"/>
+      <c r="U9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -1952,8 +2122,12 @@
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T10" s="1"/>
+      <c r="U10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -1974,8 +2148,12 @@
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T11" s="1"/>
+      <c r="U11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>167</v>
       </c>
@@ -1996,8 +2174,12 @@
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T12" s="1"/>
+      <c r="U12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>168</v>
       </c>
@@ -2018,8 +2200,12 @@
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T13" s="1"/>
+      <c r="U13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>169</v>
       </c>
@@ -2040,8 +2226,12 @@
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T14" s="1"/>
+      <c r="U14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>170</v>
       </c>
@@ -2062,8 +2252,12 @@
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>171</v>
       </c>
@@ -2084,8 +2278,12 @@
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T16" s="1"/>
+      <c r="U16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>172</v>
       </c>
@@ -2106,8 +2304,12 @@
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T17" s="1"/>
+      <c r="U17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>173</v>
       </c>
@@ -2128,12 +2330,18 @@
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T18" s="1"/>
+      <c r="U18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="K19" s="4"/>
+      <c r="K19" s="4" t="s">
+        <v>285</v>
+      </c>
       <c r="M19" s="5">
         <v>46040</v>
       </c>
@@ -2148,8 +2356,12 @@
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T19" s="1"/>
+      <c r="U19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>175</v>
       </c>
@@ -2167,8 +2379,12 @@
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T20" s="1"/>
+      <c r="U20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>176</v>
       </c>
@@ -2186,8 +2402,12 @@
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T21" s="1"/>
+      <c r="U21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>177</v>
       </c>
@@ -2205,8 +2425,12 @@
       </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T22" s="1"/>
+      <c r="U22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>178</v>
       </c>
@@ -2224,8 +2448,12 @@
       </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T23" s="1"/>
+      <c r="U23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>179</v>
       </c>
@@ -2243,8 +2471,12 @@
       </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T24" s="1"/>
+      <c r="U24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>180</v>
       </c>
@@ -2262,8 +2494,10 @@
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>181</v>
       </c>
@@ -2281,8 +2515,12 @@
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T26" s="1"/>
+      <c r="U26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>182</v>
       </c>
@@ -2300,8 +2538,12 @@
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T27" s="1"/>
+      <c r="U27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>183</v>
       </c>
@@ -2319,8 +2561,12 @@
       </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T28" s="1"/>
+      <c r="U28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>184</v>
       </c>
@@ -2338,8 +2584,12 @@
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T29" s="1"/>
+      <c r="U29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -2357,8 +2607,12 @@
       </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T30" s="1"/>
+      <c r="U30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>186</v>
       </c>
@@ -2376,8 +2630,12 @@
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T31" s="1"/>
+      <c r="U31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>187</v>
       </c>
@@ -2395,8 +2653,12 @@
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T32" s="1"/>
+      <c r="U32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>188</v>
       </c>
@@ -2414,8 +2676,12 @@
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T33" s="1"/>
+      <c r="U33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -2433,8 +2699,12 @@
       </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T34" s="1"/>
+      <c r="U34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>190</v>
       </c>
@@ -2452,8 +2722,12 @@
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T35" s="1"/>
+      <c r="U35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>191</v>
       </c>
@@ -2471,8 +2745,12 @@
       </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T36" s="1"/>
+      <c r="U36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>192</v>
       </c>
@@ -2490,8 +2768,12 @@
       </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T37" s="1"/>
+      <c r="U37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>193</v>
       </c>
@@ -2509,8 +2791,12 @@
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T38" s="1"/>
+      <c r="U38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>194</v>
       </c>
@@ -2528,8 +2814,12 @@
       </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T39" s="1"/>
+      <c r="U39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>195</v>
       </c>
@@ -2547,8 +2837,12 @@
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T40" s="1"/>
+      <c r="U40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>196</v>
       </c>
@@ -2566,8 +2860,12 @@
       </c>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T41" s="1"/>
+      <c r="U41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -2585,8 +2883,12 @@
       </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T42" s="1"/>
+      <c r="U42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -2604,8 +2906,12 @@
       </c>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T43" s="1"/>
+      <c r="U43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>199</v>
       </c>
@@ -2623,8 +2929,12 @@
       </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T44" s="1"/>
+      <c r="U44" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>200</v>
       </c>
@@ -2642,8 +2952,12 @@
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T45" s="1"/>
+      <c r="U45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>201</v>
       </c>
@@ -2661,8 +2975,12 @@
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T46" s="1"/>
+      <c r="U46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>202</v>
       </c>
@@ -2680,8 +2998,12 @@
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T47" s="1"/>
+      <c r="U47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>263</v>
       </c>
@@ -2699,8 +3021,12 @@
       </c>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T48" s="1"/>
+      <c r="U48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>264</v>
       </c>
@@ -2718,8 +3044,12 @@
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T49" s="1"/>
+      <c r="U49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>265</v>
       </c>
@@ -2737,8 +3067,12 @@
       </c>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T50" s="1"/>
+      <c r="U50" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -2756,8 +3090,12 @@
       </c>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T51" s="1"/>
+      <c r="U51" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>267</v>
       </c>
@@ -2775,8 +3113,12 @@
       </c>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T52" s="1"/>
+      <c r="U52" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>268</v>
       </c>
@@ -2794,8 +3136,10 @@
       </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>269</v>
       </c>
@@ -2813,8 +3157,10 @@
       </c>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-    </row>
-    <row r="55" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+    </row>
+    <row r="55" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M55" s="5">
         <v>46076</v>
       </c>
@@ -2829,8 +3175,12 @@
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-    </row>
-    <row r="56" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T55" s="1"/>
+      <c r="U55" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M56" s="5">
         <v>46077</v>
       </c>
@@ -2845,8 +3195,12 @@
       </c>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
-    </row>
-    <row r="57" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T56" s="1"/>
+      <c r="U56" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M57" s="5">
         <v>46078</v>
       </c>
@@ -2861,8 +3215,12 @@
       </c>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
-    </row>
-    <row r="58" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T57" s="1"/>
+      <c r="U57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M58" s="5">
         <v>46079</v>
       </c>
@@ -2877,8 +3235,12 @@
       </c>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-    </row>
-    <row r="59" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T58" s="1"/>
+      <c r="U58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M59" s="5">
         <v>46080</v>
       </c>
@@ -2893,8 +3255,12 @@
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
-    </row>
-    <row r="60" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T59" s="1"/>
+      <c r="U59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M60" s="5">
         <v>46081</v>
       </c>
@@ -2909,8 +3275,12 @@
       </c>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
-    </row>
-    <row r="61" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T60" s="1"/>
+      <c r="U60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M61" s="5">
         <v>46082</v>
       </c>
@@ -2925,8 +3295,12 @@
       </c>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
-    </row>
-    <row r="62" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T61" s="1"/>
+      <c r="U61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M62" s="5">
         <v>46083</v>
       </c>
@@ -2941,8 +3315,12 @@
       </c>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
-    </row>
-    <row r="63" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T62" s="1"/>
+      <c r="U62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M63" s="5">
         <v>46084</v>
       </c>
@@ -2957,8 +3335,12 @@
       </c>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
-    </row>
-    <row r="64" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T63" s="1"/>
+      <c r="U63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M64" s="5">
         <v>46085</v>
       </c>
@@ -2973,8 +3355,12 @@
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
-    </row>
-    <row r="65" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T64" s="1"/>
+      <c r="U64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M65" s="5">
         <v>46086</v>
       </c>
@@ -2989,8 +3375,12 @@
       </c>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
-    </row>
-    <row r="66" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T65" s="1"/>
+      <c r="U65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M66" s="5">
         <v>46087</v>
       </c>
@@ -3005,8 +3395,12 @@
       </c>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
-    </row>
-    <row r="67" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T66" s="1"/>
+      <c r="U66" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M67" s="5">
         <v>46088</v>
       </c>
@@ -3021,8 +3415,12 @@
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
-    </row>
-    <row r="68" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T67" s="1"/>
+      <c r="U67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M68" s="5">
         <v>46089</v>
       </c>
@@ -3037,8 +3435,12 @@
       </c>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
-    </row>
-    <row r="69" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T68" s="1"/>
+      <c r="U68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M69" s="5">
         <v>46090</v>
       </c>
@@ -3053,8 +3455,12 @@
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
-    </row>
-    <row r="70" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T69" s="1"/>
+      <c r="U69" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M70" s="5">
         <v>46091</v>
       </c>
@@ -3069,8 +3475,12 @@
       </c>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-    </row>
-    <row r="71" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T70" s="1"/>
+      <c r="U70" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M71" s="5">
         <v>46092</v>
       </c>
@@ -3085,8 +3495,12 @@
       </c>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
-    </row>
-    <row r="72" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T71" s="1"/>
+      <c r="U71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M72" s="5">
         <v>46093</v>
       </c>
@@ -3101,8 +3515,12 @@
       </c>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-    </row>
-    <row r="73" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T72" s="1"/>
+      <c r="U72" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M73" s="5">
         <v>46094</v>
       </c>
@@ -3117,8 +3535,12 @@
       </c>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-    </row>
-    <row r="74" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T73" s="1"/>
+      <c r="U73" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M74" s="5">
         <v>46095</v>
       </c>
@@ -3133,8 +3555,12 @@
       </c>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-    </row>
-    <row r="75" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T74" s="1"/>
+      <c r="U74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M75" s="5">
         <v>46096</v>
       </c>
@@ -3149,8 +3575,12 @@
       </c>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-    </row>
-    <row r="76" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T75" s="1"/>
+      <c r="U75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M76" s="5">
         <v>46097</v>
       </c>
@@ -3165,8 +3595,12 @@
       </c>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
-    </row>
-    <row r="77" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T76" s="1"/>
+      <c r="U76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M77" s="5">
         <v>46098</v>
       </c>
@@ -3181,8 +3615,12 @@
       </c>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
-    </row>
-    <row r="78" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T77" s="1"/>
+      <c r="U77" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M78" s="5">
         <v>46099</v>
       </c>
@@ -3197,8 +3635,12 @@
       </c>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
-    </row>
-    <row r="79" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T78" s="1"/>
+      <c r="U78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M79" s="5">
         <v>46100</v>
       </c>
@@ -3213,8 +3655,12 @@
       </c>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
-    </row>
-    <row r="80" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T79" s="1"/>
+      <c r="U79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M80" s="5">
         <v>46101</v>
       </c>
@@ -3229,8 +3675,12 @@
       </c>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
-    </row>
-    <row r="81" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T80" s="1"/>
+      <c r="U80" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M81" s="5">
         <v>46102</v>
       </c>
@@ -3245,8 +3695,12 @@
       </c>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
-    </row>
-    <row r="82" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T81" s="1"/>
+      <c r="U81" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M82" s="5">
         <v>46103</v>
       </c>
@@ -3261,8 +3715,12 @@
       </c>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
-    </row>
-    <row r="83" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T82" s="1"/>
+      <c r="U82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M83" s="5">
         <v>46104</v>
       </c>
@@ -3277,8 +3735,12 @@
       </c>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
-    </row>
-    <row r="84" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T83" s="1"/>
+      <c r="U83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M84" s="5">
         <v>46105</v>
       </c>
@@ -3293,8 +3755,12 @@
       </c>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-    </row>
-    <row r="85" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T84" s="1"/>
+      <c r="U84" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M85" s="5">
         <v>46106</v>
       </c>
@@ -3309,8 +3775,10 @@
       </c>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-    </row>
-    <row r="86" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+    </row>
+    <row r="86" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M86" s="5">
         <v>46107</v>
       </c>
@@ -3325,8 +3793,12 @@
       </c>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-    </row>
-    <row r="87" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T86" s="1"/>
+      <c r="U86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M87" s="5">
         <v>46108</v>
       </c>
@@ -3341,8 +3813,12 @@
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-    </row>
-    <row r="88" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T87" s="1"/>
+      <c r="U87" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M88" s="5">
         <v>46109</v>
       </c>
@@ -3357,8 +3833,12 @@
       </c>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-    </row>
-    <row r="89" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T88" s="1"/>
+      <c r="U88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M89" s="5">
         <v>46110</v>
       </c>
@@ -3373,8 +3853,12 @@
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-    </row>
-    <row r="90" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T89" s="1"/>
+      <c r="U89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M90" s="5">
         <v>46111</v>
       </c>
@@ -3389,8 +3873,12 @@
       </c>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-    </row>
-    <row r="91" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T90" s="1"/>
+      <c r="U90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M91" s="5">
         <v>46112</v>
       </c>
@@ -3405,8 +3893,12 @@
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-    </row>
-    <row r="92" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T91" s="1"/>
+      <c r="U91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M92" s="5">
         <v>46113</v>
       </c>
@@ -3421,8 +3913,12 @@
       </c>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-    </row>
-    <row r="93" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T92" s="1"/>
+      <c r="U92" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M93" s="5">
         <v>46114</v>
       </c>
@@ -3437,8 +3933,12 @@
       </c>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-    </row>
-    <row r="94" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T93" s="1"/>
+      <c r="U93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M94" s="5">
         <v>46115</v>
       </c>
@@ -3453,8 +3953,12 @@
       </c>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-    </row>
-    <row r="95" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T94" s="1"/>
+      <c r="U94" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M95" s="5">
         <v>46116</v>
       </c>
@@ -3469,8 +3973,12 @@
       </c>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-    </row>
-    <row r="96" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T95" s="1"/>
+      <c r="U95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M96" s="5">
         <v>46117</v>
       </c>
@@ -3485,8 +3993,12 @@
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-    </row>
-    <row r="97" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T96" s="1"/>
+      <c r="U96" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M97" s="5">
         <v>46118</v>
       </c>
@@ -3501,8 +4013,12 @@
       </c>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-    </row>
-    <row r="98" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T97" s="1"/>
+      <c r="U97" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M98" s="5">
         <v>46119</v>
       </c>
@@ -3517,8 +4033,12 @@
       </c>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-    </row>
-    <row r="99" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T98" s="1"/>
+      <c r="U98" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M99" s="5">
         <v>46120</v>
       </c>
@@ -3533,8 +4053,12 @@
       </c>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-    </row>
-    <row r="100" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T99" s="1"/>
+      <c r="U99" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M100" s="5">
         <v>46121</v>
       </c>
@@ -3549,8 +4073,12 @@
       </c>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-    </row>
-    <row r="101" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T100" s="1"/>
+      <c r="U100" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M101" s="5">
         <v>46122</v>
       </c>
@@ -3565,8 +4093,12 @@
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-    </row>
-    <row r="102" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T101" s="1"/>
+      <c r="U101" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M102" s="5">
         <v>46123</v>
       </c>
@@ -3581,8 +4113,12 @@
       </c>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-    </row>
-    <row r="103" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T102" s="1"/>
+      <c r="U102" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M103" s="5">
         <v>46124</v>
       </c>
@@ -3597,8 +4133,12 @@
       </c>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-    </row>
-    <row r="104" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T103" s="1"/>
+      <c r="U103" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M104" s="5">
         <v>46125</v>
       </c>
@@ -3613,8 +4153,12 @@
       </c>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-    </row>
-    <row r="105" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T104" s="1"/>
+      <c r="U104" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M105" s="5">
         <v>46126</v>
       </c>
@@ -3629,8 +4173,12 @@
       </c>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-    </row>
-    <row r="106" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T105" s="1"/>
+      <c r="U105" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M106" s="5">
         <v>46127</v>
       </c>
@@ -3645,8 +4193,12 @@
       </c>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-    </row>
-    <row r="107" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T106" s="1"/>
+      <c r="U106" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M107" s="5">
         <v>46128</v>
       </c>
@@ -3661,8 +4213,12 @@
       </c>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-    </row>
-    <row r="108" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T107" s="1"/>
+      <c r="U107" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M108" s="5">
         <v>46129</v>
       </c>
@@ -3677,8 +4233,12 @@
       </c>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-    </row>
-    <row r="109" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T108" s="1"/>
+      <c r="U108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M109" s="5">
         <v>46130</v>
       </c>
@@ -3693,8 +4253,12 @@
       </c>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-    </row>
-    <row r="110" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T109" s="1"/>
+      <c r="U109" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M110" s="5">
         <v>46131</v>
       </c>
@@ -3709,8 +4273,12 @@
       </c>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-    </row>
-    <row r="111" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T110" s="1"/>
+      <c r="U110" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M111" s="5">
         <v>46132</v>
       </c>
@@ -3725,8 +4293,12 @@
       </c>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-    </row>
-    <row r="112" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T111" s="1"/>
+      <c r="U111" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M112" s="5">
         <v>46133</v>
       </c>
@@ -3741,8 +4313,12 @@
       </c>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-    </row>
-    <row r="113" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T112" s="1"/>
+      <c r="U112" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M113" s="5">
         <v>46134</v>
       </c>
@@ -3757,8 +4333,12 @@
       </c>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-    </row>
-    <row r="114" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T113" s="1"/>
+      <c r="U113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M114" s="5">
         <v>46135</v>
       </c>
@@ -3773,8 +4353,12 @@
       </c>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-    </row>
-    <row r="115" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T114" s="1"/>
+      <c r="U114" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M115" s="5">
         <v>46136</v>
       </c>
@@ -3789,8 +4373,12 @@
       </c>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-    </row>
-    <row r="116" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T115" s="1"/>
+      <c r="U115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M116" s="5">
         <v>46137</v>
       </c>
@@ -3805,8 +4393,12 @@
       </c>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-    </row>
-    <row r="117" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T116" s="1"/>
+      <c r="U116" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M117" s="5">
         <v>46138</v>
       </c>
@@ -3821,8 +4413,12 @@
       </c>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-    </row>
-    <row r="118" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T117" s="1"/>
+      <c r="U117" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M118" s="5">
         <v>46139</v>
       </c>
@@ -3837,8 +4433,10 @@
       </c>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-    </row>
-    <row r="119" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T118" s="1"/>
+      <c r="U118" s="1"/>
+    </row>
+    <row r="119" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M119" s="5">
         <v>46140</v>
       </c>
@@ -3853,8 +4451,10 @@
       </c>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-    </row>
-    <row r="120" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T119" s="1"/>
+      <c r="U119" s="1"/>
+    </row>
+    <row r="120" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M120" s="5">
         <v>46141</v>
       </c>
@@ -3869,8 +4469,12 @@
       </c>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-    </row>
-    <row r="121" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T120" s="1"/>
+      <c r="U120" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M121" s="5">
         <v>46142</v>
       </c>
@@ -3885,8 +4489,12 @@
       </c>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-    </row>
-    <row r="122" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T121" s="1"/>
+      <c r="U121" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M122" s="5">
         <v>46143</v>
       </c>
@@ -3901,8 +4509,12 @@
       </c>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-    </row>
-    <row r="123" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T122" s="1"/>
+      <c r="U122" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M123" s="5">
         <v>46144</v>
       </c>
@@ -3917,8 +4529,12 @@
       </c>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-    </row>
-    <row r="124" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T123" s="1"/>
+      <c r="U123" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M124" s="5">
         <v>46145</v>
       </c>
@@ -3933,8 +4549,12 @@
       </c>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-    </row>
-    <row r="125" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T124" s="1"/>
+      <c r="U124" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M125" s="5">
         <v>46146</v>
       </c>
@@ -3949,8 +4569,12 @@
       </c>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-    </row>
-    <row r="126" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T125" s="1"/>
+      <c r="U125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M126" s="5">
         <v>46147</v>
       </c>
@@ -3965,8 +4589,12 @@
       </c>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-    </row>
-    <row r="127" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T126" s="1"/>
+      <c r="U126" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M127" s="5">
         <v>46148</v>
       </c>
@@ -3981,8 +4609,12 @@
       </c>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-    </row>
-    <row r="128" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T127" s="1"/>
+      <c r="U127" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M128" s="5">
         <v>46149</v>
       </c>
@@ -3997,8 +4629,12 @@
       </c>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-    </row>
-    <row r="129" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T128" s="1"/>
+      <c r="U128" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M129" s="5">
         <v>46150</v>
       </c>
@@ -4013,8 +4649,12 @@
       </c>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
-    </row>
-    <row r="130" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T129" s="1"/>
+      <c r="U129" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M130" s="5">
         <v>46151</v>
       </c>
@@ -4029,8 +4669,12 @@
       </c>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-    </row>
-    <row r="131" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T130" s="1"/>
+      <c r="U130" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M131" s="5">
         <v>46152</v>
       </c>
@@ -4045,8 +4689,12 @@
       </c>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-    </row>
-    <row r="132" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T131" s="1"/>
+      <c r="U131" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M132" s="5">
         <v>46153</v>
       </c>
@@ -4061,8 +4709,12 @@
       </c>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-    </row>
-    <row r="133" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T132" s="1"/>
+      <c r="U132" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M133" s="5">
         <v>46154</v>
       </c>
@@ -4077,8 +4729,12 @@
       </c>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-    </row>
-    <row r="134" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T133" s="1"/>
+      <c r="U133" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M134" s="5">
         <v>46155</v>
       </c>
@@ -4093,8 +4749,12 @@
       </c>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-    </row>
-    <row r="135" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T134" s="1"/>
+      <c r="U134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M135" s="5">
         <v>46156</v>
       </c>
@@ -4109,8 +4769,12 @@
       </c>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-    </row>
-    <row r="136" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T135" s="1"/>
+      <c r="U135" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M136" s="5">
         <v>46157</v>
       </c>
@@ -4125,8 +4789,12 @@
       </c>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-    </row>
-    <row r="137" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T136" s="1"/>
+      <c r="U136" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M137" s="5">
         <v>46158</v>
       </c>
@@ -4141,8 +4809,12 @@
       </c>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-    </row>
-    <row r="138" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T137" s="1"/>
+      <c r="U137" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M138" s="5">
         <v>46159</v>
       </c>
@@ -4157,8 +4829,12 @@
       </c>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-    </row>
-    <row r="139" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T138" s="1"/>
+      <c r="U138" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M139" s="5">
         <v>46160</v>
       </c>
@@ -4173,8 +4849,12 @@
       </c>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-    </row>
-    <row r="140" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T139" s="1"/>
+      <c r="U139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M140" s="5">
         <v>46161</v>
       </c>
@@ -4189,8 +4869,12 @@
       </c>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-    </row>
-    <row r="141" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T140" s="1"/>
+      <c r="U140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M141" s="5">
         <v>46162</v>
       </c>
@@ -4205,8 +4889,12 @@
       </c>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-    </row>
-    <row r="142" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T141" s="1"/>
+      <c r="U141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M142" s="5">
         <v>46163</v>
       </c>
@@ -4221,8 +4909,12 @@
       </c>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-    </row>
-    <row r="143" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T142" s="1"/>
+      <c r="U142" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M143" s="5">
         <v>46164</v>
       </c>
@@ -4237,8 +4929,12 @@
       </c>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-    </row>
-    <row r="144" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T143" s="1"/>
+      <c r="U143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M144" s="5">
         <v>46165</v>
       </c>
@@ -4253,8 +4949,12 @@
       </c>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-    </row>
-    <row r="145" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T144" s="1"/>
+      <c r="U144" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M145" s="5">
         <v>46166</v>
       </c>
@@ -4269,8 +4969,12 @@
       </c>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-    </row>
-    <row r="146" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T145" s="1"/>
+      <c r="U145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M146" s="5">
         <v>46167</v>
       </c>
@@ -4285,8 +4989,12 @@
       </c>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-    </row>
-    <row r="147" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T146" s="1"/>
+      <c r="U146" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M147" s="5">
         <v>46168</v>
       </c>
@@ -4301,8 +5009,12 @@
       </c>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-    </row>
-    <row r="148" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T147" s="1"/>
+      <c r="U147" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M148" s="5">
         <v>46169</v>
       </c>
@@ -4317,8 +5029,12 @@
       </c>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-    </row>
-    <row r="149" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T148" s="1"/>
+      <c r="U148" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M149" s="5">
         <v>46170</v>
       </c>
@@ -4333,8 +5049,10 @@
       </c>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-    </row>
-    <row r="150" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T149" s="1"/>
+      <c r="U149" s="1"/>
+    </row>
+    <row r="150" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M150" s="5">
         <v>46171</v>
       </c>
@@ -4349,8 +5067,12 @@
       </c>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-    </row>
-    <row r="151" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T150" s="1"/>
+      <c r="U150" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M151" s="5">
         <v>46172</v>
       </c>
@@ -4365,8 +5087,12 @@
       </c>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-    </row>
-    <row r="152" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T151" s="1"/>
+      <c r="U151" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M152" s="5">
         <v>46173</v>
       </c>
@@ -4381,8 +5107,12 @@
       </c>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-    </row>
-    <row r="153" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T152" s="1"/>
+      <c r="U152" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M153" s="5">
         <v>46174</v>
       </c>
@@ -4397,8 +5127,12 @@
       </c>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-    </row>
-    <row r="154" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T153" s="1"/>
+      <c r="U153" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M154" s="5">
         <v>46175</v>
       </c>
@@ -4413,8 +5147,12 @@
       </c>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-    </row>
-    <row r="155" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T154" s="1"/>
+      <c r="U154" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M155" s="5">
         <v>46176</v>
       </c>
@@ -4429,8 +5167,12 @@
       </c>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-    </row>
-    <row r="156" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T155" s="1"/>
+      <c r="U155" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M156" s="5">
         <v>46177</v>
       </c>
@@ -4445,8 +5187,12 @@
       </c>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-    </row>
-    <row r="157" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T156" s="1"/>
+      <c r="U156" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M157" s="5">
         <v>46178</v>
       </c>
@@ -4461,8 +5207,12 @@
       </c>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-    </row>
-    <row r="158" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T157" s="1"/>
+      <c r="U157" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M158" s="5">
         <v>46179</v>
       </c>
@@ -4477,8 +5227,12 @@
       </c>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-    </row>
-    <row r="159" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T158" s="1"/>
+      <c r="U158" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M159" s="5">
         <v>46180</v>
       </c>
@@ -4493,8 +5247,12 @@
       </c>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-    </row>
-    <row r="160" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T159" s="1"/>
+      <c r="U159" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M160" s="5">
         <v>46181</v>
       </c>
@@ -4509,8 +5267,12 @@
       </c>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
-    </row>
-    <row r="161" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T160" s="1"/>
+      <c r="U160" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M161" s="5">
         <v>46182</v>
       </c>
@@ -4525,8 +5287,12 @@
       </c>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-    </row>
-    <row r="162" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T161" s="1"/>
+      <c r="U161" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M162" s="5">
         <v>46183</v>
       </c>
@@ -4541,8 +5307,12 @@
       </c>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-    </row>
-    <row r="163" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T162" s="1"/>
+      <c r="U162" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M163" s="5">
         <v>46184</v>
       </c>
@@ -4557,8 +5327,12 @@
       </c>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-    </row>
-    <row r="164" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T163" s="1"/>
+      <c r="U163" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M164" s="5">
         <v>46185</v>
       </c>
@@ -4573,8 +5347,12 @@
       </c>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
-    </row>
-    <row r="165" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T164" s="1"/>
+      <c r="U164" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M165" s="5">
         <v>46186</v>
       </c>
@@ -4589,8 +5367,12 @@
       </c>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
-    </row>
-    <row r="166" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T165" s="1"/>
+      <c r="U165" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M166" s="5">
         <v>46187</v>
       </c>
@@ -4605,8 +5387,12 @@
       </c>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-    </row>
-    <row r="167" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T166" s="1"/>
+      <c r="U166" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M167" s="5">
         <v>46188</v>
       </c>
@@ -4621,8 +5407,12 @@
       </c>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-    </row>
-    <row r="168" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T167" s="1"/>
+      <c r="U167" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M168" s="5">
         <v>46189</v>
       </c>
@@ -4637,8 +5427,12 @@
       </c>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-    </row>
-    <row r="169" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T168" s="1"/>
+      <c r="U168" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M169" s="5">
         <v>46190</v>
       </c>
@@ -4653,8 +5447,12 @@
       </c>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-    </row>
-    <row r="170" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T169" s="1"/>
+      <c r="U169" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M170" s="5">
         <v>46191</v>
       </c>
@@ -4669,8 +5467,12 @@
       </c>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-    </row>
-    <row r="171" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T170" s="1"/>
+      <c r="U170" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M171" s="5">
         <v>46192</v>
       </c>
@@ -4685,8 +5487,12 @@
       </c>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-    </row>
-    <row r="172" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T171" s="1"/>
+      <c r="U171" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M172" s="5">
         <v>46193</v>
       </c>
@@ -4701,8 +5507,12 @@
       </c>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-    </row>
-    <row r="173" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T172" s="1"/>
+      <c r="U172" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M173" s="5">
         <v>46194</v>
       </c>
@@ -4717,8 +5527,12 @@
       </c>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-    </row>
-    <row r="174" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T173" s="1"/>
+      <c r="U173" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M174" s="5">
         <v>46195</v>
       </c>
@@ -4733,8 +5547,12 @@
       </c>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
-    </row>
-    <row r="175" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T174" s="1"/>
+      <c r="U174" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M175" s="5">
         <v>46196</v>
       </c>
@@ -4749,8 +5567,12 @@
       </c>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
-    </row>
-    <row r="176" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T175" s="1"/>
+      <c r="U175" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M176" s="5">
         <v>46197</v>
       </c>
@@ -4765,8 +5587,12 @@
       </c>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
-    </row>
-    <row r="177" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T176" s="1"/>
+      <c r="U176" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M177" s="5">
         <v>46198</v>
       </c>
@@ -4781,8 +5607,10 @@
       </c>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
-    </row>
-    <row r="178" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T177" s="1"/>
+      <c r="U177" s="1"/>
+    </row>
+    <row r="178" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M178" s="5">
         <v>46199</v>
       </c>
@@ -4797,8 +5625,10 @@
       </c>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
-    </row>
-    <row r="179" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T178" s="1"/>
+      <c r="U178" s="1"/>
+    </row>
+    <row r="179" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M179" s="5">
         <v>46200</v>
       </c>
@@ -4813,8 +5643,12 @@
       </c>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
-    </row>
-    <row r="180" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T179" s="1"/>
+      <c r="U179" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M180" s="5">
         <v>46201</v>
       </c>
@@ -4829,8 +5663,12 @@
       </c>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
-    </row>
-    <row r="181" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T180" s="1"/>
+      <c r="U180" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M181" s="5">
         <v>46202</v>
       </c>
@@ -4845,8 +5683,12 @@
       </c>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
-    </row>
-    <row r="182" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T181" s="1"/>
+      <c r="U181" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M182" s="5">
         <v>46203</v>
       </c>
@@ -4861,8 +5703,12 @@
       </c>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
-    </row>
-    <row r="183" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T182" s="1"/>
+      <c r="U182" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M183" s="5">
         <v>46204</v>
       </c>
@@ -4877,8 +5723,12 @@
       </c>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
-    </row>
-    <row r="184" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T183" s="1"/>
+      <c r="U183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M184" s="5">
         <v>46205</v>
       </c>
@@ -4893,8 +5743,12 @@
       </c>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
-    </row>
-    <row r="185" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T184" s="1"/>
+      <c r="U184" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M185" s="5">
         <v>46206</v>
       </c>
@@ -4909,8 +5763,12 @@
       </c>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
-    </row>
-    <row r="186" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T185" s="1"/>
+      <c r="U185" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M186" s="5">
         <v>46207</v>
       </c>
@@ -4925,8 +5783,12 @@
       </c>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-    </row>
-    <row r="187" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T186" s="1"/>
+      <c r="U186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M187" s="5">
         <v>46208</v>
       </c>
@@ -4941,8 +5803,12 @@
       </c>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-    </row>
-    <row r="188" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T187" s="1"/>
+      <c r="U187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M188" s="5">
         <v>46209</v>
       </c>
@@ -4957,8 +5823,12 @@
       </c>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-    </row>
-    <row r="189" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T188" s="1"/>
+      <c r="U188" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M189" s="5">
         <v>46210</v>
       </c>
@@ -4973,8 +5843,12 @@
       </c>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-    </row>
-    <row r="190" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T189" s="1"/>
+      <c r="U189" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M190" s="5">
         <v>46211</v>
       </c>
@@ -4989,8 +5863,12 @@
       </c>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-    </row>
-    <row r="191" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T190" s="1"/>
+      <c r="U190" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M191" s="5">
         <v>46212</v>
       </c>
@@ -5005,8 +5883,12 @@
       </c>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-    </row>
-    <row r="192" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T191" s="1"/>
+      <c r="U191" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M192" s="5">
         <v>46213</v>
       </c>
@@ -5021,8 +5903,12 @@
       </c>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
-    </row>
-    <row r="193" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T192" s="1"/>
+      <c r="U192" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M193" s="5">
         <v>46214</v>
       </c>
@@ -5037,8 +5923,12 @@
       </c>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
-    </row>
-    <row r="194" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T193" s="1"/>
+      <c r="U193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M194" s="5">
         <v>46215</v>
       </c>
@@ -5053,8 +5943,12 @@
       </c>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
-    </row>
-    <row r="195" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T194" s="1"/>
+      <c r="U194" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M195" s="5">
         <v>46216</v>
       </c>
@@ -5069,8 +5963,12 @@
       </c>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
-    </row>
-    <row r="196" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T195" s="1"/>
+      <c r="U195" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M196" s="5">
         <v>46217</v>
       </c>
@@ -5085,8 +5983,12 @@
       </c>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
-    </row>
-    <row r="197" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T196" s="1"/>
+      <c r="U196" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M197" s="5">
         <v>46218</v>
       </c>
@@ -5101,8 +6003,12 @@
       </c>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
-    </row>
-    <row r="198" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T197" s="1"/>
+      <c r="U197" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M198" s="5">
         <v>46219</v>
       </c>
@@ -5117,8 +6023,12 @@
       </c>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
-    </row>
-    <row r="199" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T198" s="1"/>
+      <c r="U198" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M199" s="5">
         <v>46220</v>
       </c>
@@ -5133,8 +6043,12 @@
       </c>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
-    </row>
-    <row r="200" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T199" s="1"/>
+      <c r="U199" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M200" s="5">
         <v>46221</v>
       </c>
@@ -5149,8 +6063,12 @@
       </c>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
-    </row>
-    <row r="201" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T200" s="1"/>
+      <c r="U200" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M201" s="5">
         <v>46222</v>
       </c>
@@ -5165,8 +6083,12 @@
       </c>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
-    </row>
-    <row r="202" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T201" s="1"/>
+      <c r="U201" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M202" s="5">
         <v>46223</v>
       </c>
@@ -5181,8 +6103,12 @@
       </c>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
-    </row>
-    <row r="203" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T202" s="1"/>
+      <c r="U202" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M203" s="5">
         <v>46224</v>
       </c>
@@ -5197,8 +6123,12 @@
       </c>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
-    </row>
-    <row r="204" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T203" s="1"/>
+      <c r="U203" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M204" s="5">
         <v>46225</v>
       </c>
@@ -5213,8 +6143,12 @@
       </c>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
-    </row>
-    <row r="205" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T204" s="1"/>
+      <c r="U204" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M205" s="5">
         <v>46226</v>
       </c>
@@ -5229,8 +6163,12 @@
       </c>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
-    </row>
-    <row r="206" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T205" s="1"/>
+      <c r="U205" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M206" s="5">
         <v>46227</v>
       </c>
@@ -5245,8 +6183,12 @@
       </c>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
-    </row>
-    <row r="207" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T206" s="1"/>
+      <c r="U206" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M207" s="5">
         <v>46228</v>
       </c>
@@ -5261,8 +6203,12 @@
       </c>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
-    </row>
-    <row r="208" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T207" s="1"/>
+      <c r="U207" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M208" s="5">
         <v>46229</v>
       </c>
@@ -5277,8 +6223,12 @@
       </c>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
-    </row>
-    <row r="209" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T208" s="1"/>
+      <c r="U208" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M209" s="5">
         <v>46230</v>
       </c>
@@ -5293,8 +6243,12 @@
       </c>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
-    </row>
-    <row r="210" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T209" s="1"/>
+      <c r="U209" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M210" s="5">
         <v>46231</v>
       </c>
@@ -5309,8 +6263,12 @@
       </c>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
-    </row>
-    <row r="211" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T210" s="1"/>
+      <c r="U210" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M211" s="5">
         <v>46232</v>
       </c>
@@ -5325,8 +6283,10 @@
       </c>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
-    </row>
-    <row r="212" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T211" s="1"/>
+      <c r="U211" s="1"/>
+    </row>
+    <row r="212" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M212" s="5">
         <v>46233</v>
       </c>
@@ -5341,8 +6301,12 @@
       </c>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
-    </row>
-    <row r="213" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T212" s="1"/>
+      <c r="U212" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M213" s="5">
         <v>46234</v>
       </c>
@@ -5357,8 +6321,12 @@
       </c>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
-    </row>
-    <row r="214" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T213" s="1"/>
+      <c r="U213" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M214" s="5">
         <v>46235</v>
       </c>
@@ -5373,8 +6341,12 @@
       </c>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
-    </row>
-    <row r="215" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T214" s="1"/>
+      <c r="U214" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M215" s="5">
         <v>46236</v>
       </c>
@@ -5389,8 +6361,12 @@
       </c>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-    </row>
-    <row r="216" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T215" s="1"/>
+      <c r="U215" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M216" s="5">
         <v>46237</v>
       </c>
@@ -5405,8 +6381,12 @@
       </c>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-    </row>
-    <row r="217" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T216" s="1"/>
+      <c r="U216" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M217" s="5">
         <v>46238</v>
       </c>
@@ -5421,8 +6401,12 @@
       </c>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-    </row>
-    <row r="218" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T217" s="1"/>
+      <c r="U217" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M218" s="5">
         <v>46239</v>
       </c>
@@ -5437,8 +6421,12 @@
       </c>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-    </row>
-    <row r="219" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T218" s="1"/>
+      <c r="U218" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M219" s="5">
         <v>46240</v>
       </c>
@@ -5453,8 +6441,12 @@
       </c>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-    </row>
-    <row r="220" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T219" s="1"/>
+      <c r="U219" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M220" s="5">
         <v>46241</v>
       </c>
@@ -5469,8 +6461,12 @@
       </c>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-    </row>
-    <row r="221" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T220" s="1"/>
+      <c r="U220" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M221" s="5">
         <v>46242</v>
       </c>
@@ -5485,8 +6481,12 @@
       </c>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-    </row>
-    <row r="222" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T221" s="1"/>
+      <c r="U221" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M222" s="5">
         <v>46243</v>
       </c>
@@ -5501,8 +6501,12 @@
       </c>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-    </row>
-    <row r="223" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T222" s="1"/>
+      <c r="U222" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M223" s="5">
         <v>46244</v>
       </c>
@@ -5517,8 +6521,12 @@
       </c>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-    </row>
-    <row r="224" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T223" s="1"/>
+      <c r="U223" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M224" s="5">
         <v>46245</v>
       </c>
@@ -5533,8 +6541,12 @@
       </c>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-    </row>
-    <row r="225" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T224" s="1"/>
+      <c r="U224" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M225" s="5">
         <v>46246</v>
       </c>
@@ -5549,8 +6561,12 @@
       </c>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-    </row>
-    <row r="226" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T225" s="1"/>
+      <c r="U225" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M226" s="5">
         <v>46247</v>
       </c>
@@ -5565,8 +6581,12 @@
       </c>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-    </row>
-    <row r="227" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T226" s="1"/>
+      <c r="U226" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M227" s="5">
         <v>46248</v>
       </c>
@@ -5581,8 +6601,12 @@
       </c>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-    </row>
-    <row r="228" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T227" s="1"/>
+      <c r="U227" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M228" s="5">
         <v>46249</v>
       </c>
@@ -5597,8 +6621,12 @@
       </c>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-    </row>
-    <row r="229" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T228" s="1"/>
+      <c r="U228" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M229" s="5">
         <v>46250</v>
       </c>
@@ -5613,8 +6641,12 @@
       </c>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-    </row>
-    <row r="230" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T229" s="1"/>
+      <c r="U229" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M230" s="5">
         <v>46251</v>
       </c>
@@ -5629,8 +6661,12 @@
       </c>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-    </row>
-    <row r="231" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T230" s="1"/>
+      <c r="U230" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M231" s="5">
         <v>46252</v>
       </c>
@@ -5645,8 +6681,12 @@
       </c>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-    </row>
-    <row r="232" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T231" s="1"/>
+      <c r="U231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M232" s="5">
         <v>46253</v>
       </c>
@@ -5661,8 +6701,12 @@
       </c>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-    </row>
-    <row r="233" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T232" s="1"/>
+      <c r="U232" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M233" s="5">
         <v>46254</v>
       </c>
@@ -5677,8 +6721,12 @@
       </c>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-    </row>
-    <row r="234" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T233" s="1"/>
+      <c r="U233" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M234" s="5">
         <v>46255</v>
       </c>
@@ -5693,8 +6741,12 @@
       </c>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-    </row>
-    <row r="235" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T234" s="1"/>
+      <c r="U234" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M235" s="5">
         <v>46256</v>
       </c>
@@ -5709,8 +6761,12 @@
       </c>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
-    </row>
-    <row r="236" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T235" s="1"/>
+      <c r="U235" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M236" s="5">
         <v>46257</v>
       </c>
@@ -5725,8 +6781,12 @@
       </c>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-    </row>
-    <row r="237" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T236" s="1"/>
+      <c r="U236" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M237" s="5">
         <v>46258</v>
       </c>
@@ -5741,8 +6801,12 @@
       </c>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-    </row>
-    <row r="238" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T237" s="1"/>
+      <c r="U237" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M238" s="5">
         <v>46259</v>
       </c>
@@ -5757,8 +6821,12 @@
       </c>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-    </row>
-    <row r="239" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T238" s="1"/>
+      <c r="U238" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M239" s="5"/>
       <c r="O239" s="4"/>
       <c r="Q239" s="1" t="s">
@@ -5766,8 +6834,12 @@
       </c>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-    </row>
-    <row r="240" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T239" s="1"/>
+      <c r="U239" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M240" s="5"/>
       <c r="O240" s="4"/>
       <c r="Q240" s="1" t="s">
@@ -5775,8 +6847,12 @@
       </c>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-    </row>
-    <row r="241" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T240" s="1"/>
+      <c r="U240" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M241" s="5"/>
       <c r="O241" s="4"/>
       <c r="Q241" s="3" t="s">
@@ -5784,8 +6860,10 @@
       </c>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-    </row>
-    <row r="242" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T241" s="1"/>
+      <c r="U241" s="1"/>
+    </row>
+    <row r="242" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M242" s="5"/>
       <c r="O242" s="4"/>
       <c r="Q242" s="2" t="s">
@@ -5793,8 +6871,10 @@
       </c>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-    </row>
-    <row r="243" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T242" s="1"/>
+      <c r="U242" s="1"/>
+    </row>
+    <row r="243" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M243" s="5"/>
       <c r="O243" s="4"/>
       <c r="Q243" s="1" t="s">
@@ -5802,8 +6882,12 @@
       </c>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
-    </row>
-    <row r="244" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T243" s="1"/>
+      <c r="U243" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M244" s="5"/>
       <c r="O244" s="4"/>
       <c r="Q244" s="1" t="s">
@@ -5811,8 +6895,12 @@
       </c>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
-    </row>
-    <row r="245" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T244" s="1"/>
+      <c r="U244" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M245" s="5"/>
       <c r="O245" s="4"/>
       <c r="Q245" s="1" t="s">
@@ -5820,8 +6908,12 @@
       </c>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
-    </row>
-    <row r="246" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T245" s="1"/>
+      <c r="U245" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M246" s="5"/>
       <c r="O246" s="4"/>
       <c r="Q246" s="1" t="s">
@@ -5829,8 +6921,12 @@
       </c>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-    </row>
-    <row r="247" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T246" s="1"/>
+      <c r="U246" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M247" s="5"/>
       <c r="O247" s="4"/>
       <c r="Q247" s="1" t="s">
@@ -5838,8 +6934,12 @@
       </c>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-    </row>
-    <row r="248" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T247" s="1"/>
+      <c r="U247" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M248" s="5"/>
       <c r="O248" s="4"/>
       <c r="Q248" s="1" t="s">
@@ -5847,8 +6947,12 @@
       </c>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-    </row>
-    <row r="249" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T248" s="1"/>
+      <c r="U248" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M249" s="5"/>
       <c r="O249" s="4"/>
       <c r="Q249" s="1" t="s">
@@ -5856,8 +6960,12 @@
       </c>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-    </row>
-    <row r="250" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T249" s="1"/>
+      <c r="U249" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M250" s="5"/>
       <c r="O250" s="4"/>
       <c r="Q250" s="1" t="s">
@@ -5865,8 +6973,12 @@
       </c>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-    </row>
-    <row r="251" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T250" s="1"/>
+      <c r="U250" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M251" s="5"/>
       <c r="O251" s="4"/>
       <c r="Q251" s="1" t="s">
@@ -5874,8 +6986,12 @@
       </c>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-    </row>
-    <row r="252" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T251" s="1"/>
+      <c r="U251" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M252" s="5"/>
       <c r="O252" s="4"/>
       <c r="Q252" s="1" t="s">
@@ -5883,8 +6999,12 @@
       </c>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-    </row>
-    <row r="253" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T252" s="1"/>
+      <c r="U252" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M253" s="5"/>
       <c r="O253" s="4"/>
       <c r="Q253" s="1" t="s">
@@ -5892,8 +7012,12 @@
       </c>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-    </row>
-    <row r="254" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T253" s="1"/>
+      <c r="U253" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M254" s="5"/>
       <c r="O254" s="4"/>
       <c r="Q254" s="1" t="s">
@@ -5901,8 +7025,12 @@
       </c>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-    </row>
-    <row r="255" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T254" s="1"/>
+      <c r="U254" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M255" s="5"/>
       <c r="O255" s="4"/>
       <c r="Q255" s="1" t="s">
@@ -5910,8 +7038,12 @@
       </c>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-    </row>
-    <row r="256" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T255" s="1"/>
+      <c r="U255" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M256" s="5"/>
       <c r="O256" s="4"/>
       <c r="Q256" s="1" t="s">
@@ -5919,8 +7051,12 @@
       </c>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-    </row>
-    <row r="257" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T256" s="1"/>
+      <c r="U256" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M257" s="5"/>
       <c r="O257" s="4"/>
       <c r="Q257" s="1" t="s">
@@ -5928,335 +7064,525 @@
       </c>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-    </row>
-    <row r="258" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T257" s="1"/>
+      <c r="U257" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q258" s="1" t="s">
         <v>6</v>
       </c>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-    </row>
-    <row r="259" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T258" s="1"/>
+      <c r="U258" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q259" s="1" t="s">
         <v>52</v>
       </c>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-    </row>
-    <row r="260" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T259" s="1"/>
+      <c r="U259" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q260" s="1" t="s">
         <v>51</v>
       </c>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-    </row>
-    <row r="261" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T260" s="1"/>
+      <c r="U260" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q261" s="1" t="s">
         <v>50</v>
       </c>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-    </row>
-    <row r="262" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T261" s="1"/>
+      <c r="U261" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q262" s="1" t="s">
         <v>49</v>
       </c>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-    </row>
-    <row r="263" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T262" s="1"/>
+      <c r="U262" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q263" s="1" t="s">
         <v>48</v>
       </c>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-    </row>
-    <row r="264" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T263" s="1"/>
+      <c r="U263" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q264" s="1" t="s">
         <v>47</v>
       </c>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-    </row>
-    <row r="265" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T264" s="1"/>
+      <c r="U264" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q265" s="1" t="s">
         <v>46</v>
       </c>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-    </row>
-    <row r="266" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T265" s="1"/>
+      <c r="U265" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q266" s="1" t="s">
         <v>45</v>
       </c>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-    </row>
-    <row r="267" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T266" s="1"/>
+      <c r="U266" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q267" s="1" t="s">
         <v>44</v>
       </c>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-    </row>
-    <row r="268" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T267" s="1"/>
+      <c r="U267" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q268" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-    </row>
-    <row r="269" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T268" s="1"/>
+      <c r="U268" s="1"/>
+    </row>
+    <row r="269" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q269" s="1" t="s">
         <v>43</v>
       </c>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-    </row>
-    <row r="270" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T269" s="1"/>
+      <c r="U269" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q270" s="1" t="s">
         <v>42</v>
       </c>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-    </row>
-    <row r="271" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T270" s="1"/>
+      <c r="U270" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q271" s="1" t="s">
         <v>41</v>
       </c>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-    </row>
-    <row r="272" spans="13:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T271" s="1"/>
+      <c r="U271" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="13:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q272" s="1" t="s">
         <v>40</v>
       </c>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-    </row>
-    <row r="273" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T272" s="1"/>
+      <c r="U272" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q273" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-    </row>
-    <row r="274" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T273" s="1"/>
+      <c r="U273" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q274" s="1" t="s">
         <v>38</v>
       </c>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-    </row>
-    <row r="275" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T274" s="1"/>
+      <c r="U274" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q275" s="1" t="s">
         <v>37</v>
       </c>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-    </row>
-    <row r="276" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T275" s="1"/>
+      <c r="U275" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q276" s="1" t="s">
         <v>0</v>
       </c>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-    </row>
-    <row r="277" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T276" s="1"/>
+      <c r="U276" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q277" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-    </row>
-    <row r="278" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T277" s="1"/>
+      <c r="U277" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q278" s="1" t="s">
         <v>36</v>
       </c>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-    </row>
-    <row r="279" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T278" s="1"/>
+      <c r="U278" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q279" s="1" t="s">
         <v>35</v>
       </c>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-    </row>
-    <row r="280" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T279" s="1"/>
+      <c r="U279" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q280" s="1" t="s">
         <v>34</v>
       </c>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-    </row>
-    <row r="281" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T280" s="1"/>
+      <c r="U280" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q281" s="1" t="s">
         <v>33</v>
       </c>
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
-    </row>
-    <row r="282" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T281" s="1"/>
+      <c r="U281" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q282" s="1" t="s">
         <v>32</v>
       </c>
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
-    </row>
-    <row r="283" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T282" s="1"/>
+      <c r="U282" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q283" s="1" t="s">
         <v>31</v>
       </c>
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
-    </row>
-    <row r="284" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T283" s="1"/>
+      <c r="U283" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q284" s="1" t="s">
         <v>30</v>
       </c>
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
-    </row>
-    <row r="285" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T284" s="1"/>
+      <c r="U284" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q285" s="1" t="s">
         <v>29</v>
       </c>
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
-    </row>
-    <row r="286" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T285" s="1"/>
+      <c r="U285" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q286" s="1" t="s">
         <v>28</v>
       </c>
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
-    </row>
-    <row r="287" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T286" s="1"/>
+      <c r="U286" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q287" s="1" t="s">
         <v>27</v>
       </c>
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
-    </row>
-    <row r="288" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T287" s="1"/>
+      <c r="U287" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q288" s="1" t="s">
         <v>26</v>
       </c>
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
-    </row>
-    <row r="289" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T288" s="1"/>
+      <c r="U288" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q289" s="1" t="s">
         <v>25</v>
       </c>
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
-    </row>
-    <row r="290" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T289" s="1"/>
+      <c r="U289" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q290" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
-    </row>
-    <row r="291" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T290" s="1"/>
+      <c r="U290" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q291" s="1" t="s">
         <v>23</v>
       </c>
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
-    </row>
-    <row r="292" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T291" s="1"/>
+      <c r="U291" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q292" s="1" t="s">
         <v>22</v>
       </c>
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
-    </row>
-    <row r="293" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T292" s="1"/>
+      <c r="U292" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q293" s="1" t="s">
         <v>21</v>
       </c>
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
-    </row>
-    <row r="294" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T293" s="1"/>
+      <c r="U293" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q294" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
-    </row>
-    <row r="295" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T294" s="1"/>
+      <c r="U294" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q295" s="1" t="s">
         <v>19</v>
       </c>
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
-    </row>
-    <row r="296" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T295" s="1"/>
+      <c r="U295" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q296" s="1" t="s">
         <v>18</v>
       </c>
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
-    </row>
-    <row r="297" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T296" s="1"/>
+      <c r="U296" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q297" s="1" t="s">
         <v>17</v>
       </c>
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
-    </row>
-    <row r="298" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T297" s="1"/>
+      <c r="U297" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q298" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
-    </row>
-    <row r="299" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T298" s="1"/>
+      <c r="U298" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q299" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
-    </row>
-    <row r="300" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T299" s="1"/>
+      <c r="U299" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q300" s="1" t="s">
         <v>14</v>
       </c>
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
-    </row>
-    <row r="301" spans="17:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T300" s="1"/>
+      <c r="U300" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="17:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q301" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
-    </row>
-    <row r="302" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T301" s="1"/>
+      <c r="U301" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q302" s="1" t="s">
         <v>12</v>
       </c>
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
-    </row>
-    <row r="303" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T302" s="1"/>
+      <c r="U302" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q303" s="1" t="s">
         <v>11</v>
       </c>
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
-    </row>
-    <row r="304" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T303" s="1"/>
+      <c r="U303" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q304" s="1" t="s">
         <v>10</v>
       </c>
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
+      <c r="T304" s="1"/>
+      <c r="U304" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="305" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q305" s="1" t="s">
@@ -6264,6 +7590,8 @@
       </c>
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
+      <c r="T305" s="1"/>
+      <c r="U305" s="1"/>
     </row>
     <row r="306" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q306" s="3" t="s">
@@ -6271,6 +7599,8 @@
       </c>
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
+      <c r="T306" s="1"/>
+      <c r="U306" s="1"/>
     </row>
     <row r="307" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q307" s="2" t="s">
@@ -6278,7 +7608,8 @@
       </c>
       <c r="R307" s="13"/>
       <c r="S307" s="13"/>
-      <c r="U307" s="14"/>
+      <c r="T307" s="1"/>
+      <c r="U307" s="19"/>
     </row>
     <row r="308" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q308" s="1" t="s">
@@ -6290,7 +7621,12 @@
       <c r="S308" s="1">
         <v>30</v>
       </c>
-      <c r="U308" s="14"/>
+      <c r="T308" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U308" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W308" s="14"/>
     </row>
     <row r="309" spans="17:23" x14ac:dyDescent="0.3">
@@ -6303,7 +7639,12 @@
       <c r="S309" s="1">
         <v>70</v>
       </c>
-      <c r="U309" s="14"/>
+      <c r="T309" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U309" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W309" s="14"/>
     </row>
     <row r="310" spans="17:23" x14ac:dyDescent="0.3">
@@ -6316,7 +7657,12 @@
       <c r="S310" s="1">
         <v>30</v>
       </c>
-      <c r="U310" s="14"/>
+      <c r="T310" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U310" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W310" s="14"/>
     </row>
     <row r="311" spans="17:23" x14ac:dyDescent="0.3">
@@ -6329,7 +7675,12 @@
       <c r="S311" s="1">
         <v>30</v>
       </c>
-      <c r="U311" s="14"/>
+      <c r="T311" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U311" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W311" s="14"/>
     </row>
     <row r="312" spans="17:23" x14ac:dyDescent="0.3">
@@ -6342,7 +7693,12 @@
       <c r="S312" s="1">
         <v>70</v>
       </c>
-      <c r="U312" s="14"/>
+      <c r="T312" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U312" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W312" s="14"/>
     </row>
     <row r="313" spans="17:23" x14ac:dyDescent="0.3">
@@ -6355,7 +7711,12 @@
       <c r="S313" s="1">
         <v>70</v>
       </c>
-      <c r="U313" s="14"/>
+      <c r="T313" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U313" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W313" s="14"/>
     </row>
     <row r="314" spans="17:23" x14ac:dyDescent="0.3">
@@ -6368,7 +7729,12 @@
       <c r="S314" s="1">
         <v>70</v>
       </c>
-      <c r="U314" s="14"/>
+      <c r="T314" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U314" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W314" s="14"/>
     </row>
     <row r="315" spans="17:23" x14ac:dyDescent="0.3">
@@ -6381,7 +7747,12 @@
       <c r="S315" s="1">
         <v>30</v>
       </c>
-      <c r="U315" s="14"/>
+      <c r="T315" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U315" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W315" s="14"/>
     </row>
     <row r="316" spans="17:23" x14ac:dyDescent="0.3">
@@ -6394,7 +7765,12 @@
       <c r="S316" s="1">
         <v>20</v>
       </c>
-      <c r="U316" s="14"/>
+      <c r="T316" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U316" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W316" s="14"/>
     </row>
     <row r="317" spans="17:23" x14ac:dyDescent="0.3">
@@ -6407,7 +7783,12 @@
       <c r="S317" s="1">
         <v>15</v>
       </c>
-      <c r="U317" s="14"/>
+      <c r="T317" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U317" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W317" s="14"/>
     </row>
     <row r="318" spans="17:23" x14ac:dyDescent="0.3">
@@ -6420,7 +7801,12 @@
       <c r="S318" s="1">
         <v>20</v>
       </c>
-      <c r="U318" s="14"/>
+      <c r="T318" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U318" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W318" s="14"/>
     </row>
     <row r="319" spans="17:23" x14ac:dyDescent="0.3">
@@ -6433,7 +7819,12 @@
       <c r="S319" s="1">
         <v>50</v>
       </c>
-      <c r="U319" s="14"/>
+      <c r="T319" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U319" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W319" s="14"/>
     </row>
     <row r="320" spans="17:23" x14ac:dyDescent="0.3">
@@ -6446,7 +7837,12 @@
       <c r="S320" s="1">
         <v>20</v>
       </c>
-      <c r="U320" s="14"/>
+      <c r="T320" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U320" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W320" s="14"/>
     </row>
     <row r="321" spans="17:23" x14ac:dyDescent="0.3">
@@ -6459,7 +7855,12 @@
       <c r="S321" s="1">
         <v>20</v>
       </c>
-      <c r="U321" s="14"/>
+      <c r="T321" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U321" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W321" s="14"/>
     </row>
     <row r="322" spans="17:23" x14ac:dyDescent="0.3">
@@ -6472,7 +7873,12 @@
       <c r="S322" s="1">
         <v>40</v>
       </c>
-      <c r="U322" s="14"/>
+      <c r="T322" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U322" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="W322" s="14"/>
     </row>
     <row r="323" spans="17:23" x14ac:dyDescent="0.3">
@@ -6485,7 +7891,13 @@
       <c r="S323" s="1">
         <v>16</v>
       </c>
-      <c r="U323" s="14"/>
+      <c r="T323" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="U323" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W323" s="21"/>
     </row>
     <row r="324" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q324" s="1" t="s">
@@ -6497,6 +7909,13 @@
       <c r="S324" s="1">
         <v>60</v>
       </c>
+      <c r="T324" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U324" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W324" s="21"/>
     </row>
     <row r="325" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q325" s="1" t="s">
@@ -6508,6 +7927,13 @@
       <c r="S325" s="1">
         <v>20</v>
       </c>
+      <c r="T325" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U325" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W325" s="21"/>
     </row>
     <row r="326" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q326" s="1" t="s">
@@ -6519,6 +7945,13 @@
       <c r="S326" s="1">
         <v>30</v>
       </c>
+      <c r="T326" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U326" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W326" s="21"/>
     </row>
     <row r="327" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q327" s="1" t="s">
@@ -6530,6 +7963,13 @@
       <c r="S327" s="1">
         <v>30</v>
       </c>
+      <c r="T327" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="U327" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W327" s="21"/>
     </row>
     <row r="328" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q328" s="1" t="s">
@@ -6541,6 +7981,13 @@
       <c r="S328" s="1">
         <v>20</v>
       </c>
+      <c r="T328" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U328" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W328" s="21"/>
     </row>
     <row r="329" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q329" s="1" t="s">
@@ -6552,6 +7999,13 @@
       <c r="S329" s="1">
         <v>7</v>
       </c>
+      <c r="T329" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U329" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W329" s="21"/>
     </row>
     <row r="330" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q330" s="1" t="s">
@@ -6563,6 +8017,13 @@
       <c r="S330" s="1">
         <v>30</v>
       </c>
+      <c r="T330" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="U330" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W330" s="21"/>
     </row>
     <row r="331" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q331" s="1" t="s">
@@ -6574,6 +8035,13 @@
       <c r="S331" s="1">
         <v>30</v>
       </c>
+      <c r="T331" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U331" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W331" s="21"/>
     </row>
     <row r="332" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q332" s="1" t="s">
@@ -6585,6 +8053,13 @@
       <c r="S332" s="1">
         <v>18</v>
       </c>
+      <c r="T332" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="U332" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W332" s="21"/>
     </row>
     <row r="333" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q333" s="1" t="s">
@@ -6596,6 +8071,13 @@
       <c r="S333" s="1">
         <v>10</v>
       </c>
+      <c r="T333" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="U333" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W333" s="21"/>
     </row>
     <row r="334" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q334" s="1" t="s">
@@ -6607,6 +8089,13 @@
       <c r="S334" s="1">
         <v>50</v>
       </c>
+      <c r="T334" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U334" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W334" s="21"/>
     </row>
     <row r="335" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q335" s="1" t="s">
@@ -6618,6 +8107,13 @@
       <c r="S335" s="1">
         <v>15</v>
       </c>
+      <c r="T335" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="U335" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W335" s="21"/>
     </row>
     <row r="336" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q336" s="1" t="s">
@@ -6629,8 +8125,15 @@
       <c r="S336" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="337" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="T336" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="U336" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W336" s="21"/>
+    </row>
+    <row r="337" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q337" s="1" t="s">
         <v>56</v>
       </c>
@@ -6640,8 +8143,15 @@
       <c r="S337" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="338" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="T337" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U337" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W337" s="21"/>
+    </row>
+    <row r="338" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q338" s="1" t="s">
         <v>209</v>
       </c>
@@ -6651,15 +8161,24 @@
       <c r="S338" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="339" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="T338" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="U338" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W338" s="21"/>
+    </row>
+    <row r="339" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q339" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
-    </row>
-    <row r="340" spans="17:22" x14ac:dyDescent="0.3">
+      <c r="T339" s="1"/>
+      <c r="U339" s="19"/>
+    </row>
+    <row r="340" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q340" s="1" t="s">
         <v>2</v>
       </c>
@@ -6669,9 +8188,15 @@
       <c r="S340" s="1">
         <v>40</v>
       </c>
+      <c r="T340" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U340" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V340" s="14"/>
     </row>
-    <row r="341" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="341" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q341" s="1" t="s">
         <v>1</v>
       </c>
@@ -6681,9 +8206,15 @@
       <c r="S341" s="1">
         <v>30</v>
       </c>
+      <c r="T341" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U341" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V341" s="14"/>
     </row>
-    <row r="342" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="342" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q342" s="1" t="s">
         <v>210</v>
       </c>
@@ -6693,9 +8224,15 @@
       <c r="S342" s="1">
         <v>15</v>
       </c>
+      <c r="T342" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U342" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V342" s="14"/>
     </row>
-    <row r="343" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="343" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q343" s="1" t="s">
         <v>0</v>
       </c>
@@ -6705,9 +8242,15 @@
       <c r="S343" s="1">
         <v>40</v>
       </c>
+      <c r="T343" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U343" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V343" s="14"/>
     </row>
-    <row r="344" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="344" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q344" s="1" t="s">
         <v>36</v>
       </c>
@@ -6717,9 +8260,15 @@
       <c r="S344" s="1">
         <v>20</v>
       </c>
+      <c r="T344" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U344" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V344" s="14"/>
     </row>
-    <row r="345" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="345" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q345" s="1" t="s">
         <v>35</v>
       </c>
@@ -6729,9 +8278,15 @@
       <c r="S345" s="1">
         <v>20</v>
       </c>
+      <c r="T345" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U345" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V345" s="14"/>
     </row>
-    <row r="346" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="346" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q346" s="1" t="s">
         <v>32</v>
       </c>
@@ -6741,9 +8296,15 @@
       <c r="S346" s="1">
         <v>50</v>
       </c>
+      <c r="T346" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U346" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V346" s="14"/>
     </row>
-    <row r="347" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="347" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q347" s="1" t="s">
         <v>73</v>
       </c>
@@ -6753,9 +8314,15 @@
       <c r="S347" s="1">
         <v>20</v>
       </c>
+      <c r="T347" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U347" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V347" s="14"/>
     </row>
-    <row r="348" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="348" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q348" s="1" t="s">
         <v>211</v>
       </c>
@@ -6765,9 +8332,15 @@
       <c r="S348" s="1">
         <v>15</v>
       </c>
+      <c r="T348" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U348" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V348" s="14"/>
     </row>
-    <row r="349" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="349" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q349" s="1" t="s">
         <v>212</v>
       </c>
@@ -6777,9 +8350,15 @@
       <c r="S349" s="1">
         <v>15</v>
       </c>
+      <c r="T349" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U349" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V349" s="14"/>
     </row>
-    <row r="350" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="350" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q350" s="1" t="s">
         <v>213</v>
       </c>
@@ -6789,9 +8368,15 @@
       <c r="S350" s="1">
         <v>15</v>
       </c>
+      <c r="T350" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U350" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V350" s="14"/>
     </row>
-    <row r="351" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="351" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q351" s="1" t="s">
         <v>30</v>
       </c>
@@ -6801,9 +8386,15 @@
       <c r="S351" s="1">
         <v>40</v>
       </c>
+      <c r="T351" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U351" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V351" s="14"/>
     </row>
-    <row r="352" spans="17:22" x14ac:dyDescent="0.3">
+    <row r="352" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q352" s="1" t="s">
         <v>18</v>
       </c>
@@ -6812,6 +8403,12 @@
       </c>
       <c r="S352" s="1">
         <v>70</v>
+      </c>
+      <c r="T352" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U352" s="19" t="b">
+        <v>1</v>
       </c>
       <c r="V352" s="14"/>
     </row>
@@ -6825,6 +8422,12 @@
       <c r="S353" s="1">
         <v>70</v>
       </c>
+      <c r="T353" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U353" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V353" s="14"/>
     </row>
     <row r="354" spans="17:23" x14ac:dyDescent="0.3">
@@ -6837,6 +8440,12 @@
       <c r="S354" s="1">
         <v>70</v>
       </c>
+      <c r="T354" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U354" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V354" s="14"/>
     </row>
     <row r="355" spans="17:23" x14ac:dyDescent="0.3">
@@ -6849,6 +8458,12 @@
       <c r="S355" s="1">
         <v>20</v>
       </c>
+      <c r="T355" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U355" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V355" s="14"/>
     </row>
     <row r="356" spans="17:23" x14ac:dyDescent="0.3">
@@ -6861,6 +8476,12 @@
       <c r="S356" s="1">
         <v>20</v>
       </c>
+      <c r="T356" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U356" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V356" s="14"/>
     </row>
     <row r="357" spans="17:23" x14ac:dyDescent="0.3">
@@ -6873,6 +8494,12 @@
       <c r="S357" s="1">
         <v>20</v>
       </c>
+      <c r="T357" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U357" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V357" s="14"/>
     </row>
     <row r="358" spans="17:23" x14ac:dyDescent="0.3">
@@ -6885,6 +8512,12 @@
       <c r="S358" s="1">
         <v>15</v>
       </c>
+      <c r="T358" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U358" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V358" s="15"/>
       <c r="W358" s="15"/>
     </row>
@@ -6898,6 +8531,12 @@
       <c r="S359" s="1">
         <v>15</v>
       </c>
+      <c r="T359" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U359" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V359" s="15"/>
       <c r="W359" s="15"/>
     </row>
@@ -6911,8 +8550,14 @@
       <c r="S360" s="1">
         <v>30</v>
       </c>
+      <c r="T360" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U360" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V360" s="15"/>
-      <c r="W360" s="15"/>
+      <c r="W360" s="18"/>
     </row>
     <row r="361" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q361" s="1" t="s">
@@ -6924,8 +8569,14 @@
       <c r="S361" s="1">
         <v>7</v>
       </c>
+      <c r="T361" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="U361" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V361" s="15"/>
-      <c r="W361" s="15"/>
+      <c r="W361" s="18"/>
     </row>
     <row r="362" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q362" s="1" t="s">
@@ -6937,8 +8588,14 @@
       <c r="S362" s="1">
         <v>8</v>
       </c>
+      <c r="T362" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U362" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V362" s="15"/>
-      <c r="W362" s="15"/>
+      <c r="W362" s="18"/>
     </row>
     <row r="363" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q363" s="1" t="s">
@@ -6950,8 +8607,14 @@
       <c r="S363" s="1">
         <v>13</v>
       </c>
+      <c r="T363" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U363" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V363" s="15"/>
-      <c r="W363" s="15"/>
+      <c r="W363" s="18"/>
     </row>
     <row r="364" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q364" s="1" t="s">
@@ -6963,8 +8626,14 @@
       <c r="S364" s="1">
         <v>50</v>
       </c>
+      <c r="T364" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U364" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V364" s="15"/>
-      <c r="W364" s="15"/>
+      <c r="W364" s="18"/>
     </row>
     <row r="365" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q365" s="1" t="s">
@@ -6976,8 +8645,14 @@
       <c r="S365" s="1">
         <v>10</v>
       </c>
+      <c r="T365" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U365" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V365" s="15"/>
-      <c r="W365" s="15"/>
+      <c r="W365" s="18"/>
     </row>
     <row r="366" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q366" s="1" t="s">
@@ -6989,8 +8664,14 @@
       <c r="S366" s="1">
         <v>20</v>
       </c>
+      <c r="T366" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U366" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V366" s="15"/>
-      <c r="W366" s="15"/>
+      <c r="W366" s="18"/>
     </row>
     <row r="367" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q367" s="1" t="s">
@@ -7002,8 +8683,14 @@
       <c r="S367" s="1">
         <v>15</v>
       </c>
+      <c r="T367" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U367" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V367" s="15"/>
-      <c r="W367" s="15"/>
+      <c r="W367" s="18"/>
     </row>
     <row r="368" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q368" s="1" t="s">
@@ -7015,8 +8702,14 @@
       <c r="S368" s="1">
         <v>30</v>
       </c>
+      <c r="T368" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U368" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V368" s="15"/>
-      <c r="W368" s="15"/>
+      <c r="W368" s="18"/>
     </row>
     <row r="369" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q369" s="1" t="s">
@@ -7028,8 +8721,14 @@
       <c r="S369" s="1">
         <v>20</v>
       </c>
+      <c r="T369" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U369" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V369" s="15"/>
-      <c r="W369" s="15"/>
+      <c r="W369" s="18"/>
     </row>
     <row r="370" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q370" s="1" t="s">
@@ -7041,8 +8740,14 @@
       <c r="S370" s="1">
         <v>50</v>
       </c>
+      <c r="T370" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U370" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V370" s="15"/>
-      <c r="W370" s="15"/>
+      <c r="W370" s="18"/>
     </row>
     <row r="371" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q371" s="1" t="s">
@@ -7054,8 +8759,14 @@
       <c r="S371" s="1">
         <v>18</v>
       </c>
+      <c r="T371" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="U371" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V371" s="15"/>
-      <c r="W371" s="15"/>
+      <c r="W371" s="18"/>
     </row>
     <row r="372" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q372" s="1" t="s">
@@ -7067,8 +8778,14 @@
       <c r="S372" s="1">
         <v>40</v>
       </c>
+      <c r="T372" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U372" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V372" s="15"/>
-      <c r="W372" s="15"/>
+      <c r="W372" s="18"/>
     </row>
     <row r="373" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q373" s="1" t="s">
@@ -7080,6 +8797,13 @@
       <c r="S373" s="1">
         <v>15</v>
       </c>
+      <c r="T373" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="U373" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W373" s="18"/>
     </row>
     <row r="374" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q374" s="1" t="s">
@@ -7091,6 +8815,13 @@
       <c r="S374" s="1">
         <v>20</v>
       </c>
+      <c r="T374" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U374" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W374" s="18"/>
     </row>
     <row r="375" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q375" s="3" t="s">
@@ -7098,6 +8829,8 @@
       </c>
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
+      <c r="T375" s="1"/>
+      <c r="U375" s="1"/>
     </row>
     <row r="376" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q376" s="13" t="s">
@@ -7105,6 +8838,8 @@
       </c>
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
+      <c r="T376" s="1"/>
+      <c r="U376" s="1"/>
     </row>
     <row r="377" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q377" s="1" t="s">
@@ -7116,6 +8851,12 @@
       <c r="S377" s="1">
         <v>70</v>
       </c>
+      <c r="T377" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U377" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="378" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q378" s="1" t="s">
@@ -7127,6 +8868,12 @@
       <c r="S378" s="1">
         <v>50</v>
       </c>
+      <c r="T378" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U378" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="379" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q379" s="1" t="s">
@@ -7138,6 +8885,12 @@
       <c r="S379" s="1">
         <v>70</v>
       </c>
+      <c r="T379" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U379" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="380" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q380" s="1" t="s">
@@ -7149,6 +8902,12 @@
       <c r="S380" s="1">
         <v>70</v>
       </c>
+      <c r="T380" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U380" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="381" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q381" s="1" t="s">
@@ -7160,6 +8919,12 @@
       <c r="S381" s="1">
         <v>30</v>
       </c>
+      <c r="T381" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U381" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="382" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q382" s="1" t="s">
@@ -7171,6 +8936,12 @@
       <c r="S382" s="1">
         <v>30</v>
       </c>
+      <c r="T382" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U382" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="383" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q383" s="1" t="s">
@@ -7182,6 +8953,12 @@
       <c r="S383" s="1">
         <v>30</v>
       </c>
+      <c r="T383" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U383" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="384" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q384" s="1" t="s">
@@ -7193,8 +8970,14 @@
       <c r="S384" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="385" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T384" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U384" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q385" s="1" t="s">
         <v>221</v>
       </c>
@@ -7204,8 +8987,14 @@
       <c r="S385" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="386" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T385" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U385" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q386" s="1" t="s">
         <v>222</v>
       </c>
@@ -7215,8 +9004,14 @@
       <c r="S386" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="387" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T386" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U386" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q387" s="1" t="s">
         <v>223</v>
       </c>
@@ -7226,8 +9021,14 @@
       <c r="S387" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="388" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T387" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U387" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q388" s="1" t="s">
         <v>224</v>
       </c>
@@ -7237,8 +9038,14 @@
       <c r="S388" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="389" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T388" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U388" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q389" s="1" t="s">
         <v>5</v>
       </c>
@@ -7248,8 +9055,14 @@
       <c r="S389" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="390" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T389" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U389" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q390" s="1" t="s">
         <v>51</v>
       </c>
@@ -7259,8 +9072,14 @@
       <c r="S390" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="391" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T390" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U390" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q391" s="1" t="s">
         <v>203</v>
       </c>
@@ -7270,8 +9089,14 @@
       <c r="S391" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="392" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T391" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U391" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q392" s="1" t="s">
         <v>225</v>
       </c>
@@ -7281,8 +9106,15 @@
       <c r="S392" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="393" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T392" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U392" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W392" s="18"/>
+    </row>
+    <row r="393" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q393" s="1" t="s">
         <v>226</v>
       </c>
@@ -7292,8 +9124,15 @@
       <c r="S393" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="394" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T393" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U393" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W393" s="18"/>
+    </row>
+    <row r="394" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q394" s="1" t="s">
         <v>44</v>
       </c>
@@ -7303,8 +9142,15 @@
       <c r="S394" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="395" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T394" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U394" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W394" s="18"/>
+    </row>
+    <row r="395" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q395" s="1" t="s">
         <v>64</v>
       </c>
@@ -7314,8 +9160,15 @@
       <c r="S395" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="396" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T395" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="U395" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W395" s="18"/>
+    </row>
+    <row r="396" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q396" s="1" t="s">
         <v>227</v>
       </c>
@@ -7325,8 +9178,15 @@
       <c r="S396" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="397" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T396" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="U396" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W396" s="18"/>
+    </row>
+    <row r="397" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q397" s="1" t="s">
         <v>61</v>
       </c>
@@ -7336,8 +9196,15 @@
       <c r="S397" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="398" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T397" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="U397" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W397" s="18"/>
+    </row>
+    <row r="398" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q398" s="1" t="s">
         <v>57</v>
       </c>
@@ -7347,8 +9214,15 @@
       <c r="S398" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="399" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T398" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="U398" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W398" s="18"/>
+    </row>
+    <row r="399" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q399" s="1" t="s">
         <v>205</v>
       </c>
@@ -7358,8 +9232,15 @@
       <c r="S399" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="400" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T399" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="U399" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W399" s="18"/>
+    </row>
+    <row r="400" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q400" s="1" t="s">
         <v>206</v>
       </c>
@@ -7369,8 +9250,15 @@
       <c r="S400" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="401" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T400" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U400" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W400" s="18"/>
+    </row>
+    <row r="401" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q401" s="1" t="s">
         <v>55</v>
       </c>
@@ -7380,8 +9268,15 @@
       <c r="S401" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="402" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T401" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U401" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W401" s="18"/>
+    </row>
+    <row r="402" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q402" s="1" t="s">
         <v>59</v>
       </c>
@@ -7391,8 +9286,15 @@
       <c r="S402" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="403" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T402" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U402" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W402" s="18"/>
+    </row>
+    <row r="403" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q403" s="1" t="s">
         <v>58</v>
       </c>
@@ -7402,8 +9304,15 @@
       <c r="S403" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="404" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T403" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="U403" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W403" s="18"/>
+    </row>
+    <row r="404" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q404" s="1" t="s">
         <v>56</v>
       </c>
@@ -7413,8 +9322,14 @@
       <c r="S404" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="405" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T404" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U404" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q405" s="1" t="s">
         <v>208</v>
       </c>
@@ -7424,8 +9339,14 @@
       <c r="S405" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="406" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T405" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U405" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q406" s="1" t="s">
         <v>228</v>
       </c>
@@ -7435,15 +9356,25 @@
       <c r="S406" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="407" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T406" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U406" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q407" s="13" t="s">
         <v>3</v>
       </c>
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
-    </row>
-    <row r="408" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T407" s="1"/>
+      <c r="U407" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="17:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q408" s="1" t="s">
         <v>0</v>
       </c>
@@ -7453,8 +9384,15 @@
       <c r="S408" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="409" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T408" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U408" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W408" s="18"/>
+    </row>
+    <row r="409" spans="17:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q409" s="1" t="s">
         <v>36</v>
       </c>
@@ -7464,8 +9402,15 @@
       <c r="S409" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="410" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T409" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U409" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W409" s="18"/>
+    </row>
+    <row r="410" spans="17:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q410" s="1" t="s">
         <v>32</v>
       </c>
@@ -7475,8 +9420,15 @@
       <c r="S410" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="411" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T410" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U410" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W410" s="18"/>
+    </row>
+    <row r="411" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q411" s="1" t="s">
         <v>73</v>
       </c>
@@ -7486,8 +9438,14 @@
       <c r="S411" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="412" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T411" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U411" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q412" s="1" t="s">
         <v>211</v>
       </c>
@@ -7497,8 +9455,14 @@
       <c r="S412" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="413" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T412" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U412" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q413" s="1" t="s">
         <v>212</v>
       </c>
@@ -7508,8 +9472,14 @@
       <c r="S413" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="414" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T413" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U413" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q414" s="1" t="s">
         <v>213</v>
       </c>
@@ -7519,8 +9489,14 @@
       <c r="S414" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="415" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T414" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U414" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q415" s="1" t="s">
         <v>18</v>
       </c>
@@ -7530,8 +9506,14 @@
       <c r="S415" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="416" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T415" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U415" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q416" s="1" t="s">
         <v>25</v>
       </c>
@@ -7540,6 +9522,12 @@
       </c>
       <c r="S416" s="1">
         <v>40</v>
+      </c>
+      <c r="T416" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U416" s="19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="17:23" x14ac:dyDescent="0.3">
@@ -7552,6 +9540,12 @@
       <c r="S417" s="1">
         <v>70</v>
       </c>
+      <c r="T417" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U417" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="418" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q418" s="1" t="s">
@@ -7563,6 +9557,12 @@
       <c r="S418" s="1">
         <v>22</v>
       </c>
+      <c r="T418" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U418" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="419" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q419" s="1" t="s">
@@ -7574,6 +9574,13 @@
       <c r="S419" s="1">
         <v>22</v>
       </c>
+      <c r="T419" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U419" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W419" s="18"/>
     </row>
     <row r="420" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q420" s="1" t="s">
@@ -7585,6 +9592,13 @@
       <c r="S420" s="1">
         <v>40</v>
       </c>
+      <c r="T420" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U420" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W420" s="18"/>
     </row>
     <row r="421" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q421" s="1" t="s">
@@ -7596,6 +9610,13 @@
       <c r="S421" s="1">
         <v>40</v>
       </c>
+      <c r="T421" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U421" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W421" s="18"/>
     </row>
     <row r="422" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q422" s="1" t="s">
@@ -7607,6 +9628,13 @@
       <c r="S422" s="1">
         <v>40</v>
       </c>
+      <c r="T422" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U422" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W422" s="18"/>
     </row>
     <row r="423" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q423" s="1" t="s">
@@ -7618,8 +9646,14 @@
       <c r="S423" s="1">
         <v>5</v>
       </c>
+      <c r="T423" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="U423" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V423" s="16"/>
-      <c r="W423" s="16"/>
+      <c r="W423" s="20"/>
     </row>
     <row r="424" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q424" s="1" t="s">
@@ -7631,8 +9665,14 @@
       <c r="S424" s="1">
         <v>40</v>
       </c>
+      <c r="T424" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="U424" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V424" s="17"/>
-      <c r="W424" s="17"/>
+      <c r="W424" s="20"/>
     </row>
     <row r="425" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q425" s="1" t="s">
@@ -7644,8 +9684,14 @@
       <c r="S425" s="1">
         <v>7</v>
       </c>
+      <c r="T425" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U425" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V425" s="17"/>
-      <c r="W425" s="17"/>
+      <c r="W425" s="20"/>
     </row>
     <row r="426" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q426" s="1" t="s">
@@ -7657,8 +9703,14 @@
       <c r="S426" s="1">
         <v>8</v>
       </c>
+      <c r="T426" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U426" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V426" s="17"/>
-      <c r="W426" s="17"/>
+      <c r="W426" s="20"/>
     </row>
     <row r="427" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q427" s="1" t="s">
@@ -7670,8 +9722,14 @@
       <c r="S427" s="1">
         <v>50</v>
       </c>
+      <c r="T427" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U427" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V427" s="17"/>
-      <c r="W427" s="17"/>
+      <c r="W427" s="20"/>
     </row>
     <row r="428" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q428" s="1" t="s">
@@ -7683,8 +9741,14 @@
       <c r="S428" s="1">
         <v>3</v>
       </c>
+      <c r="T428" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U428" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V428" s="17"/>
-      <c r="W428" s="17"/>
+      <c r="W428" s="20"/>
     </row>
     <row r="429" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q429" s="1" t="s">
@@ -7696,8 +9760,14 @@
       <c r="S429" s="1">
         <v>20</v>
       </c>
+      <c r="T429" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U429" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V429" s="17"/>
-      <c r="W429" s="17"/>
+      <c r="W429" s="20"/>
     </row>
     <row r="430" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q430" s="1" t="s">
@@ -7709,8 +9779,14 @@
       <c r="S430" s="1">
         <v>20</v>
       </c>
+      <c r="T430" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U430" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V430" s="17"/>
-      <c r="W430" s="17"/>
+      <c r="W430" s="20"/>
     </row>
     <row r="431" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q431" s="1" t="s">
@@ -7722,8 +9798,14 @@
       <c r="S431" s="1">
         <v>5</v>
       </c>
+      <c r="T431" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="U431" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V431" s="17"/>
-      <c r="W431" s="17"/>
+      <c r="W431" s="20"/>
     </row>
     <row r="432" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q432" s="1" t="s">
@@ -7735,8 +9817,14 @@
       <c r="S432" s="1">
         <v>5</v>
       </c>
+      <c r="T432" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="U432" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V432" s="16"/>
-      <c r="W432" s="16"/>
+      <c r="W432" s="20"/>
     </row>
     <row r="433" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q433" s="1" t="s">
@@ -7748,8 +9836,14 @@
       <c r="S433" s="1">
         <v>40</v>
       </c>
+      <c r="T433" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U433" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V433" s="17"/>
-      <c r="W433" s="17"/>
+      <c r="W433" s="20"/>
     </row>
     <row r="434" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q434" s="1" t="s">
@@ -7761,8 +9855,14 @@
       <c r="S434" s="1">
         <v>18</v>
       </c>
+      <c r="T434" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="U434" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V434" s="17"/>
-      <c r="W434" s="17"/>
+      <c r="W434" s="20"/>
     </row>
     <row r="435" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q435" s="1" t="s">
@@ -7774,8 +9874,14 @@
       <c r="S435" s="1">
         <v>50</v>
       </c>
+      <c r="T435" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U435" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V435" s="17"/>
-      <c r="W435" s="17"/>
+      <c r="W435" s="20"/>
     </row>
     <row r="436" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q436" s="1" t="s">
@@ -7787,8 +9893,14 @@
       <c r="S436" s="1">
         <v>50</v>
       </c>
+      <c r="T436" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U436" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V436" s="17"/>
-      <c r="W436" s="17"/>
+      <c r="W436" s="20"/>
     </row>
     <row r="437" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q437" s="1" t="s">
@@ -7800,8 +9912,14 @@
       <c r="S437" s="1">
         <v>17</v>
       </c>
+      <c r="T437" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U437" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V437" s="17"/>
-      <c r="W437" s="17"/>
+      <c r="W437" s="20"/>
     </row>
     <row r="438" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q438" s="1" t="s">
@@ -7813,8 +9931,14 @@
       <c r="S438" s="1">
         <v>30</v>
       </c>
+      <c r="T438" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U438" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V438" s="17"/>
-      <c r="W438" s="17"/>
+      <c r="W438" s="20"/>
     </row>
     <row r="439" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q439" s="1" t="s">
@@ -7826,8 +9950,14 @@
       <c r="S439" s="1">
         <v>12</v>
       </c>
+      <c r="T439" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="U439" s="19" t="b">
+        <v>1</v>
+      </c>
       <c r="V439" s="17"/>
-      <c r="W439" s="17"/>
+      <c r="W439" s="20"/>
     </row>
     <row r="440" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q440" s="3" t="s">
@@ -7835,6 +9965,8 @@
       </c>
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
+      <c r="T440" s="1"/>
+      <c r="U440" s="1"/>
     </row>
     <row r="441" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q441" s="13" t="s">
@@ -7842,6 +9974,8 @@
       </c>
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
+      <c r="T441" s="1"/>
+      <c r="U441" s="1"/>
     </row>
     <row r="442" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q442" s="1" t="s">
@@ -7853,6 +9987,12 @@
       <c r="S442" s="1">
         <v>50</v>
       </c>
+      <c r="T442" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U442" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="443" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q443" s="1" t="s">
@@ -7864,6 +10004,12 @@
       <c r="S443" s="1">
         <v>40</v>
       </c>
+      <c r="T443" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U443" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="444" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q444" s="1" t="s">
@@ -7875,6 +10021,12 @@
       <c r="S444" s="1">
         <v>70</v>
       </c>
+      <c r="T444" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U444" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="445" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q445" s="1" t="s">
@@ -7886,6 +10038,12 @@
       <c r="S445" s="1">
         <v>70</v>
       </c>
+      <c r="T445" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U445" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="446" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q446" s="1" t="s">
@@ -7897,6 +10055,12 @@
       <c r="S446" s="1">
         <v>30</v>
       </c>
+      <c r="T446" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U446" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="447" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q447" s="1" t="s">
@@ -7908,6 +10072,12 @@
       <c r="S447" s="1">
         <v>30</v>
       </c>
+      <c r="T447" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U447" s="19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="448" spans="17:23" x14ac:dyDescent="0.3">
       <c r="Q448" s="1" t="s">
@@ -7919,8 +10089,14 @@
       <c r="S448" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="449" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T448" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U448" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q449" s="1" t="s">
         <v>219</v>
       </c>
@@ -7930,8 +10106,14 @@
       <c r="S449" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="450" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T449" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U449" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q450" s="1" t="s">
         <v>220</v>
       </c>
@@ -7941,8 +10123,14 @@
       <c r="S450" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="451" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T450" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U450" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q451" s="1" t="s">
         <v>221</v>
       </c>
@@ -7952,8 +10140,14 @@
       <c r="S451" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="452" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T451" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U451" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q452" s="1" t="s">
         <v>222</v>
       </c>
@@ -7963,8 +10157,14 @@
       <c r="S452" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="453" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T452" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U452" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q453" s="1" t="s">
         <v>223</v>
       </c>
@@ -7974,8 +10174,14 @@
       <c r="S453" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="454" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T453" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U453" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q454" s="1" t="s">
         <v>224</v>
       </c>
@@ -7985,8 +10191,14 @@
       <c r="S454" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="455" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T454" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U454" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q455" s="1" t="s">
         <v>5</v>
       </c>
@@ -7996,8 +10208,14 @@
       <c r="S455" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="456" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T455" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U455" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q456" s="1" t="s">
         <v>242</v>
       </c>
@@ -8007,8 +10225,14 @@
       <c r="S456" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="457" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T456" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U456" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q457" s="1" t="s">
         <v>203</v>
       </c>
@@ -8018,8 +10242,14 @@
       <c r="S457" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="458" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T457" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U457" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q458" s="1" t="s">
         <v>225</v>
       </c>
@@ -8029,8 +10259,14 @@
       <c r="S458" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="459" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T458" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U458" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q459" s="1" t="s">
         <v>226</v>
       </c>
@@ -8040,8 +10276,14 @@
       <c r="S459" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="460" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T459" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U459" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q460" s="1" t="s">
         <v>44</v>
       </c>
@@ -8051,8 +10293,14 @@
       <c r="S460" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="461" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T460" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U460" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q461" s="1" t="s">
         <v>243</v>
       </c>
@@ -8062,8 +10310,14 @@
       <c r="S461" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="462" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T461" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="U461" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q462" s="1" t="s">
         <v>64</v>
       </c>
@@ -8073,8 +10327,14 @@
       <c r="S462" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="463" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T462" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U462" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q463" s="1" t="s">
         <v>244</v>
       </c>
@@ -8084,8 +10344,14 @@
       <c r="S463" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="464" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T463" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="U463" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q464" s="1" t="s">
         <v>61</v>
       </c>
@@ -8095,8 +10361,14 @@
       <c r="S464" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="465" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T464" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="U464" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q465" s="1" t="s">
         <v>59</v>
       </c>
@@ -8106,8 +10378,14 @@
       <c r="S465" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="466" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T465" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U465" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q466" s="1" t="s">
         <v>245</v>
       </c>
@@ -8117,8 +10395,14 @@
       <c r="S466" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="467" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T466" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="U466" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q467" s="1" t="s">
         <v>57</v>
       </c>
@@ -8128,8 +10412,14 @@
       <c r="S467" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="468" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T467" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U467" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q468" s="1" t="s">
         <v>205</v>
       </c>
@@ -8139,8 +10429,14 @@
       <c r="S468" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="469" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T468" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="U468" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q469" s="1" t="s">
         <v>206</v>
       </c>
@@ -8150,8 +10446,14 @@
       <c r="S469" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="470" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T469" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U469" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q470" s="1" t="s">
         <v>55</v>
       </c>
@@ -8161,8 +10463,14 @@
       <c r="S470" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="471" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T470" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U470" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q471" s="1" t="s">
         <v>58</v>
       </c>
@@ -8172,8 +10480,14 @@
       <c r="S471" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="472" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T471" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="U471" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q472" s="1" t="s">
         <v>56</v>
       </c>
@@ -8183,8 +10497,14 @@
       <c r="S472" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="473" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T472" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="U472" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q473" s="1" t="s">
         <v>208</v>
       </c>
@@ -8194,8 +10514,14 @@
       <c r="S473" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="474" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T473" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U473" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q474" s="1" t="s">
         <v>228</v>
       </c>
@@ -8205,8 +10531,14 @@
       <c r="S474" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="475" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T474" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="U474" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q475" s="1" t="s">
         <v>246</v>
       </c>
@@ -8216,15 +10548,23 @@
       <c r="S475" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="476" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T475" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U475" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q476" s="13" t="s">
         <v>3</v>
       </c>
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
-    </row>
-    <row r="477" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T476" s="1"/>
+      <c r="U476" s="1"/>
+    </row>
+    <row r="477" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q477" s="1" t="s">
         <v>36</v>
       </c>
@@ -8234,8 +10574,14 @@
       <c r="S477" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="478" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T477" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U477" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q478" s="1" t="s">
         <v>32</v>
       </c>
@@ -8245,8 +10591,14 @@
       <c r="S478" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="479" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T478" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U478" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q479" s="1" t="s">
         <v>73</v>
       </c>
@@ -8256,8 +10608,14 @@
       <c r="S479" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="480" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T479" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U479" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q480" s="1" t="s">
         <v>211</v>
       </c>
@@ -8267,8 +10625,14 @@
       <c r="S480" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="481" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T480" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U480" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q481" s="1" t="s">
         <v>212</v>
       </c>
@@ -8278,8 +10642,14 @@
       <c r="S481" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="482" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T481" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U481" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q482" s="1" t="s">
         <v>213</v>
       </c>
@@ -8289,8 +10659,14 @@
       <c r="S482" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="483" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T482" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U482" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q483" s="1" t="s">
         <v>18</v>
       </c>
@@ -8300,8 +10676,14 @@
       <c r="S483" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="484" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T483" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U483" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q484" s="1" t="s">
         <v>24</v>
       </c>
@@ -8311,8 +10693,14 @@
       <c r="S484" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="485" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T484" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U484" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q485" s="1" t="s">
         <v>229</v>
       </c>
@@ -8322,8 +10710,14 @@
       <c r="S485" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="486" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T485" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U485" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q486" s="1" t="s">
         <v>230</v>
       </c>
@@ -8333,8 +10727,14 @@
       <c r="S486" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="487" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T486" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U486" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q487" s="1" t="s">
         <v>19</v>
       </c>
@@ -8344,8 +10744,14 @@
       <c r="S487" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="488" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T487" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U487" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q488" s="1" t="s">
         <v>15</v>
       </c>
@@ -8355,8 +10761,14 @@
       <c r="S488" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="489" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T488" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U488" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q489" s="1" t="s">
         <v>14</v>
       </c>
@@ -8366,8 +10778,14 @@
       <c r="S489" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="490" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T489" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U489" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q490" s="1" t="s">
         <v>231</v>
       </c>
@@ -8377,8 +10795,14 @@
       <c r="S490" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="491" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T490" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="U490" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q491" s="1" t="s">
         <v>247</v>
       </c>
@@ -8388,8 +10812,14 @@
       <c r="S491" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="492" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T491" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="U491" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q492" s="1" t="s">
         <v>214</v>
       </c>
@@ -8399,8 +10829,14 @@
       <c r="S492" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="493" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T492" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U492" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q493" s="1" t="s">
         <v>248</v>
       </c>
@@ -8410,8 +10846,14 @@
       <c r="S493" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="494" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T493" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U493" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q494" s="1" t="s">
         <v>216</v>
       </c>
@@ -8421,8 +10863,14 @@
       <c r="S494" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="495" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T494" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U494" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q495" s="1" t="s">
         <v>232</v>
       </c>
@@ -8432,8 +10880,14 @@
       <c r="S495" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="496" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T495" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U495" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q496" s="1" t="s">
         <v>249</v>
       </c>
@@ -8443,8 +10897,14 @@
       <c r="S496" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="497" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T496" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="U496" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q497" s="1" t="s">
         <v>43</v>
       </c>
@@ -8454,8 +10914,14 @@
       <c r="S497" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="498" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T497" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U497" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q498" s="1" t="s">
         <v>26</v>
       </c>
@@ -8465,8 +10931,14 @@
       <c r="S498" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="499" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T498" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U498" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="17:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q499" s="1" t="s">
         <v>22</v>
       </c>
@@ -8476,8 +10948,14 @@
       <c r="S499" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="500" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T499" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="U499" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q500" s="1" t="s">
         <v>21</v>
       </c>
@@ -8487,8 +10965,14 @@
       <c r="S500" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="501" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T500" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U500" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q501" s="1" t="s">
         <v>217</v>
       </c>
@@ -8498,8 +10982,14 @@
       <c r="S501" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="502" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T501" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U501" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q502" s="1" t="s">
         <v>250</v>
       </c>
@@ -8509,8 +10999,14 @@
       <c r="S502" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="503" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T502" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="U502" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q503" s="1" t="s">
         <v>251</v>
       </c>
@@ -8520,8 +11016,14 @@
       <c r="S503" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="504" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T503" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U503" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q504" s="1" t="s">
         <v>20</v>
       </c>
@@ -8531,8 +11033,14 @@
       <c r="S504" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="505" spans="17:19" x14ac:dyDescent="0.3">
+      <c r="T504" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="U504" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="17:21" x14ac:dyDescent="0.3">
       <c r="Q505" s="1" t="s">
         <v>234</v>
       </c>
@@ -8541,6 +11049,12 @@
       </c>
       <c r="S505" s="1">
         <v>6</v>
+      </c>
+      <c r="T505" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="U505" s="19" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Inspeccion Labores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C45E21-58A5-473B-AF33-D44AF2A4B2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78602440-660D-4799-B982-E24E367DB5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11051,7 +11051,7 @@
         <v>6</v>
       </c>
       <c r="T505" s="1" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="U505" s="19" t="b">
         <v>1</v>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Inspeccion Labores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78602440-660D-4799-B982-E24E367DB5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7B0F28B-F5FE-4C30-B38C-54CE86EE40D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1073,7 +1073,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1125,6 +1125,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10938,7 +10941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="17:21" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="17:21" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q499" s="1" t="s">
         <v>22</v>
       </c>
@@ -10948,7 +10951,7 @@
       <c r="S499" s="1">
         <v>50</v>
       </c>
-      <c r="T499" s="1" t="s">
+      <c r="T499" s="22" t="s">
         <v>294</v>
       </c>
       <c r="U499" s="19" t="b">
